--- a/Control de pagos Farmavisa.xlsx
+++ b/Control de pagos Farmavisa.xlsx
@@ -8,18 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Farmavisa_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD9CBD9F-0504-4A6F-8309-AB2BD9E8D160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E8E81F8-E4FF-4E25-9FBA-6E77229269C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="874" xr2:uid="{BEA16B71-FE3A-4F3E-BD5F-E87CB848FD8F}"/>
   </bookViews>
   <sheets>
     <sheet name="Programación de pagos" sheetId="6" r:id="rId1"/>
+    <sheet name="NO TOCAR" sheetId="5" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programación de pagos'!$A$1:$H$617</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programación de pagos'!$A$1:$H$637</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +38,7 @@
     <author>USER</author>
   </authors>
   <commentList>
-    <comment ref="E55" authorId="0" shapeId="0" xr:uid="{272611C1-7E99-485C-8D18-0D034A23AC68}">
+    <comment ref="E55" authorId="0" shapeId="0" xr:uid="{9F3229D5-A431-4F77-861D-AD4880120CCC}">
       <text>
         <r>
           <rPr>
@@ -64,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E77" authorId="0" shapeId="0" xr:uid="{A6877C42-D667-4159-ADEF-EFDCD12E0D53}">
+    <comment ref="E77" authorId="0" shapeId="0" xr:uid="{775F1805-C083-4817-8834-B31CC3B1D859}">
       <text>
         <r>
           <rPr>
@@ -88,7 +86,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E82" authorId="0" shapeId="0" xr:uid="{BCC30352-6F16-46B8-B30E-4BD3ECFD0605}">
+    <comment ref="E82" authorId="0" shapeId="0" xr:uid="{EB010995-D879-4357-B664-BD82A630FF74}">
       <text>
         <r>
           <rPr>
@@ -112,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E86" authorId="0" shapeId="0" xr:uid="{A41B5C1E-5E41-44E9-9CDE-1C2B867CA075}">
+    <comment ref="E86" authorId="0" shapeId="0" xr:uid="{988DACFA-8CBD-4EB9-B9BC-D0FC84FA7B0E}">
       <text>
         <r>
           <rPr>
@@ -137,7 +135,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E163" authorId="1" shapeId="0" xr:uid="{99374558-666B-458A-B71A-381AE53E6AB7}">
+    <comment ref="E163" authorId="1" shapeId="0" xr:uid="{77287020-3203-4352-9744-93F48CA0C2BF}">
       <text>
         <r>
           <rPr>
@@ -160,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2822" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2858" uniqueCount="261">
   <si>
     <t>Luz Nelly</t>
   </si>
@@ -522,6 +520,9 @@
     <t>fijo</t>
   </si>
   <si>
+    <t>TOTAL:</t>
+  </si>
+  <si>
     <t>Espuma</t>
   </si>
   <si>
@@ -741,6 +742,15 @@
     <t>junio</t>
   </si>
   <si>
+    <t>Total pagado mes:</t>
+  </si>
+  <si>
+    <t>Total Facturado mes:</t>
+  </si>
+  <si>
+    <t>Diferencia:</t>
+  </si>
+  <si>
     <t>F-V 24706</t>
   </si>
   <si>
@@ -885,6 +895,9 @@
     <t>F-V 24565</t>
   </si>
   <si>
+    <t>26/06/2026</t>
+  </si>
+  <si>
     <t>F-V 23851</t>
   </si>
   <si>
@@ -906,31 +919,28 @@
     <t>F-V-25670</t>
   </si>
   <si>
+    <t>F-V-25880</t>
+  </si>
+  <si>
+    <t>F-V-25945</t>
+  </si>
+  <si>
+    <t>31/09/2026</t>
+  </si>
+  <si>
     <t>F-V-25803</t>
   </si>
   <si>
-    <t>F-V-25880</t>
-  </si>
-  <si>
     <t>F-V-26004</t>
   </si>
   <si>
     <t>F-V-26081</t>
   </si>
   <si>
-    <t>F-V-25945</t>
-  </si>
-  <si>
-    <t>TOTAL:</t>
-  </si>
-  <si>
-    <t>Total pagado mes:</t>
-  </si>
-  <si>
-    <t>Total Facturado mes:</t>
-  </si>
-  <si>
-    <t>Diferencia:</t>
+    <t>F-V-26225</t>
+  </si>
+  <si>
+    <t>F-V-26318</t>
   </si>
 </sst>
 </file>
@@ -939,9 +949,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_-[$$-240A]\ * #,##0_-;\-[$$-240A]\ * #,##0_-;_-[$$-240A]\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="_-[$$-240A]\ * #,##0.00_-;\-[$$-240A]\ * #,##0.00_-;_-[$$-240A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1084,10 +1094,10 @@
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1164,6 +1174,9 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1176,16 +1189,22 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1212,39 +1231,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Programación de pagos"/>
-      <sheetName val="Contro de Caja"/>
-      <sheetName val="Sacar precio"/>
-      <sheetName val="Arqueo de Caja General"/>
-      <sheetName val="Arqueo de Caja"/>
-      <sheetName val="Raya"/>
-      <sheetName val="NO TOCAR"/>
-      <sheetName val="Hoja1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7">
-        <row r="81">
-          <cell r="E81">
-            <v>10153733</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1544,7 +1530,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{906D2921-3C88-4305-B420-E819C8736A5E}">
-  <dimension ref="A1:J641"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:J643"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" style="6" bestFit="1" customWidth="1"/>
@@ -1585,7 +1572,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>14</v>
       </c>
@@ -1715,7 +1702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>18</v>
       </c>
@@ -1737,7 +1724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>18</v>
       </c>
@@ -3789,7 +3776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
         <v>23</v>
       </c>
@@ -3815,7 +3802,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>29</v>
       </c>
@@ -3841,7 +3828,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="11" t="s">
         <v>29</v>
       </c>
@@ -3867,7 +3854,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
         <v>26</v>
       </c>
@@ -3893,7 +3880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
         <v>27</v>
       </c>
@@ -3919,7 +3906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>30</v>
       </c>
@@ -3945,7 +3932,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="11" t="s">
         <v>32</v>
       </c>
@@ -3972,7 +3959,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="11" t="s">
         <v>33</v>
       </c>
@@ -3998,7 +3985,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="11" t="s">
         <v>35</v>
       </c>
@@ -4024,7 +4011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
         <v>0</v>
       </c>
@@ -4050,7 +4037,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
         <v>5</v>
       </c>
@@ -4076,7 +4063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="11" t="s">
         <v>1</v>
       </c>
@@ -4102,7 +4089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="11" t="s">
         <v>37</v>
       </c>
@@ -4128,7 +4115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="11" t="s">
         <v>33</v>
       </c>
@@ -4147,14 +4134,14 @@
       <c r="F100" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="33">
+      <c r="G100" s="32">
         <v>45945</v>
       </c>
       <c r="H100" s="11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
         <v>1</v>
       </c>
@@ -4180,7 +4167,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="11" t="s">
         <v>37</v>
       </c>
@@ -4206,7 +4193,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
         <v>29</v>
       </c>
@@ -4232,7 +4219,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="11" t="s">
         <v>29</v>
       </c>
@@ -4259,7 +4246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="11" t="s">
         <v>29</v>
       </c>
@@ -4285,7 +4272,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
         <v>29</v>
       </c>
@@ -4312,7 +4299,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="11" t="s">
         <v>29</v>
       </c>
@@ -4338,7 +4325,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="11" t="s">
         <v>29</v>
       </c>
@@ -4364,7 +4351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="11" t="s">
         <v>29</v>
       </c>
@@ -4390,7 +4377,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
         <v>29</v>
       </c>
@@ -4416,7 +4403,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
         <v>29</v>
       </c>
@@ -4443,7 +4430,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
         <v>39</v>
       </c>
@@ -4469,7 +4456,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
         <v>0</v>
       </c>
@@ -4495,7 +4482,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
         <v>5</v>
       </c>
@@ -4521,7 +4508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
         <v>1</v>
       </c>
@@ -4547,7 +4534,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="11" t="s">
         <v>37</v>
       </c>
@@ -4573,7 +4560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
         <v>33</v>
       </c>
@@ -4599,7 +4586,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
         <v>32</v>
       </c>
@@ -4626,7 +4613,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
         <v>29</v>
       </c>
@@ -4653,7 +4640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
         <v>29</v>
       </c>
@@ -4679,7 +4666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
         <v>29</v>
       </c>
@@ -4705,7 +4692,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
         <v>29</v>
       </c>
@@ -4732,7 +4719,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
         <v>29</v>
       </c>
@@ -4758,7 +4745,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
         <v>29</v>
       </c>
@@ -4785,7 +4772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
         <v>39</v>
       </c>
@@ -4811,7 +4798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
         <v>27</v>
       </c>
@@ -4837,7 +4824,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
         <v>32</v>
       </c>
@@ -4864,7 +4851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
         <v>32</v>
       </c>
@@ -4891,7 +4878,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
         <v>30</v>
       </c>
@@ -4917,7 +4904,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
         <v>26</v>
       </c>
@@ -4943,7 +4930,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
         <v>35</v>
       </c>
@@ -4969,7 +4956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
         <v>0</v>
       </c>
@@ -4995,7 +4982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
         <v>1</v>
       </c>
@@ -5021,7 +5008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
         <v>37</v>
       </c>
@@ -5047,7 +5034,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
         <v>33</v>
       </c>
@@ -5073,7 +5060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
         <v>29</v>
       </c>
@@ -5099,7 +5086,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
         <v>29</v>
       </c>
@@ -5126,7 +5113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
         <v>29</v>
       </c>
@@ -5168,7 +5155,7 @@
       <c r="E139" s="4">
         <v>241139</v>
       </c>
-      <c r="F139" s="28" t="s">
+      <c r="F139" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G139" s="12">
@@ -5194,7 +5181,7 @@
       <c r="E140" s="4">
         <v>732700</v>
       </c>
-      <c r="F140" s="28" t="s">
+      <c r="F140" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G140" s="12">
@@ -5220,7 +5207,7 @@
       <c r="E141" s="4">
         <v>34600</v>
       </c>
-      <c r="F141" s="28" t="s">
+      <c r="F141" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G141" s="12">
@@ -5237,7 +5224,7 @@
       <c r="B142" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C142" s="11" t="s">
+      <c r="C142" s="26" t="s">
         <v>46</v>
       </c>
       <c r="D142" s="12">
@@ -5246,7 +5233,7 @@
       <c r="E142" s="4">
         <v>720500</v>
       </c>
-      <c r="F142" s="29" t="s">
+      <c r="F142" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G142" s="12">
@@ -5256,7 +5243,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
         <v>32</v>
       </c>
@@ -5290,7 +5277,7 @@
       <c r="B144" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C144" s="11" t="s">
+      <c r="C144" s="26" t="s">
         <v>47</v>
       </c>
       <c r="D144" s="12">
@@ -5299,7 +5286,7 @@
       <c r="E144" s="4">
         <v>1230166</v>
       </c>
-      <c r="F144" s="29" t="s">
+      <c r="F144" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G144" s="12">
@@ -5309,7 +5296,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
         <v>29</v>
       </c>
@@ -5342,7 +5329,7 @@
       <c r="B146" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C146" s="11" t="s">
+      <c r="C146" s="26" t="s">
         <v>48</v>
       </c>
       <c r="D146" s="12">
@@ -5351,7 +5338,7 @@
       <c r="E146" s="4">
         <v>1127700</v>
       </c>
-      <c r="F146" s="29" t="s">
+      <c r="F146" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G146" s="12">
@@ -5361,7 +5348,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
         <v>0</v>
       </c>
@@ -5387,7 +5374,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
         <v>1</v>
       </c>
@@ -5413,7 +5400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
         <v>37</v>
       </c>
@@ -5439,7 +5426,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
         <v>33</v>
       </c>
@@ -5465,7 +5452,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
         <v>29</v>
       </c>
@@ -5492,7 +5479,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
         <v>29</v>
       </c>
@@ -5525,7 +5512,7 @@
       <c r="B153" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C153" s="11" t="s">
+      <c r="C153" s="26" t="s">
         <v>49</v>
       </c>
       <c r="D153" s="12">
@@ -5534,7 +5521,7 @@
       <c r="E153" s="4">
         <v>1440950</v>
       </c>
-      <c r="F153" s="28" t="s">
+      <c r="F153" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G153" s="12">
@@ -5552,7 +5539,7 @@
       <c r="B154" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C154" s="11" t="s">
+      <c r="C154" s="26" t="s">
         <v>51</v>
       </c>
       <c r="D154" s="12">
@@ -5561,7 +5548,7 @@
       <c r="E154" s="4">
         <v>1450460</v>
       </c>
-      <c r="F154" s="29" t="s">
+      <c r="F154" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G154" s="12">
@@ -5571,7 +5558,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
         <v>39</v>
       </c>
@@ -5597,7 +5584,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
         <v>27</v>
       </c>
@@ -5623,7 +5610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="11" t="s">
         <v>0</v>
       </c>
@@ -5649,7 +5636,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
         <v>1</v>
       </c>
@@ -5675,7 +5662,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
         <v>30</v>
       </c>
@@ -5701,7 +5688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
         <v>26</v>
       </c>
@@ -5734,7 +5721,7 @@
       <c r="B161" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C161" s="11" t="s">
+      <c r="C161" s="26" t="s">
         <v>53</v>
       </c>
       <c r="D161" s="12">
@@ -5743,7 +5730,7 @@
       <c r="E161" s="4">
         <v>1493600</v>
       </c>
-      <c r="F161" s="29" t="s">
+      <c r="F161" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G161" s="12">
@@ -5760,7 +5747,7 @@
       <c r="B162" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C162" s="11" t="s">
+      <c r="C162" s="26" t="s">
         <v>54</v>
       </c>
       <c r="D162" s="12">
@@ -5769,7 +5756,7 @@
       <c r="E162" s="4">
         <v>715400</v>
       </c>
-      <c r="F162" s="28" t="s">
+      <c r="F162" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G162" s="12">
@@ -5779,7 +5766,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="11" t="s">
         <v>116</v>
       </c>
@@ -5802,7 +5789,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="11" t="s">
         <v>35</v>
       </c>
@@ -5828,7 +5815,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="11" t="s">
         <v>0</v>
       </c>
@@ -5854,7 +5841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="11" t="s">
         <v>1</v>
       </c>
@@ -5880,7 +5867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="11" t="s">
         <v>37</v>
       </c>
@@ -5906,7 +5893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="11" t="s">
         <v>37</v>
       </c>
@@ -5932,7 +5919,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="11" t="s">
         <v>33</v>
       </c>
@@ -5958,7 +5945,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="11" t="s">
         <v>33</v>
       </c>
@@ -5989,7 +5976,7 @@
       <c r="B171" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C171" s="11" t="s">
+      <c r="C171" s="26" t="s">
         <v>55</v>
       </c>
       <c r="D171" s="12">
@@ -5998,7 +5985,7 @@
       <c r="E171" s="4">
         <v>1210300</v>
       </c>
-      <c r="F171" s="28" t="s">
+      <c r="F171" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G171" s="12">
@@ -6015,7 +6002,7 @@
       <c r="B172" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C172" s="11" t="s">
+      <c r="C172" s="26" t="s">
         <v>56</v>
       </c>
       <c r="D172" s="12">
@@ -6024,7 +6011,7 @@
       <c r="E172" s="4">
         <v>86400</v>
       </c>
-      <c r="F172" s="28" t="s">
+      <c r="F172" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G172" s="12">
@@ -6041,7 +6028,7 @@
       <c r="B173" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C173" s="11" t="s">
+      <c r="C173" s="26" t="s">
         <v>57</v>
       </c>
       <c r="D173" s="12">
@@ -6050,7 +6037,7 @@
       <c r="E173" s="4">
         <v>663765</v>
       </c>
-      <c r="F173" s="29" t="s">
+      <c r="F173" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G173" s="12">
@@ -6067,7 +6054,7 @@
       <c r="B174" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C174" s="11" t="s">
+      <c r="C174" s="26" t="s">
         <v>58</v>
       </c>
       <c r="D174" s="12">
@@ -6076,7 +6063,7 @@
       <c r="E174" s="4">
         <v>1603450</v>
       </c>
-      <c r="F174" s="29" t="s">
+      <c r="F174" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G174" s="12">
@@ -6086,7 +6073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="11" t="s">
         <v>39</v>
       </c>
@@ -6112,7 +6099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="11" t="s">
         <v>39</v>
       </c>
@@ -6138,7 +6125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="11" t="s">
         <v>29</v>
       </c>
@@ -6165,7 +6152,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="11" t="s">
         <v>29</v>
       </c>
@@ -6192,7 +6179,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="11" t="s">
         <v>29</v>
       </c>
@@ -6219,7 +6206,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="11" t="s">
         <v>29</v>
       </c>
@@ -6245,7 +6232,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="11" t="s">
         <v>29</v>
       </c>
@@ -6279,7 +6266,7 @@
       <c r="B182" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C182" s="11" t="s">
+      <c r="C182" s="26" t="s">
         <v>59</v>
       </c>
       <c r="D182" s="12">
@@ -6288,7 +6275,7 @@
       <c r="E182" s="4">
         <v>1282960</v>
       </c>
-      <c r="F182" s="28" t="s">
+      <c r="F182" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G182" s="12">
@@ -6305,7 +6292,7 @@
       <c r="B183" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C183" s="11" t="s">
+      <c r="C183" s="26" t="s">
         <v>60</v>
       </c>
       <c r="D183" s="12">
@@ -6314,7 +6301,7 @@
       <c r="E183" s="4">
         <v>330900</v>
       </c>
-      <c r="F183" s="28" t="s">
+      <c r="F183" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G183" s="12">
@@ -6331,7 +6318,7 @@
       <c r="B184" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C184" s="11" t="s">
+      <c r="C184" s="26" t="s">
         <v>61</v>
       </c>
       <c r="D184" s="12">
@@ -6340,7 +6327,7 @@
       <c r="E184" s="4">
         <v>1218100</v>
       </c>
-      <c r="F184" s="29" t="s">
+      <c r="F184" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G184" s="12">
@@ -6357,7 +6344,7 @@
       <c r="B185" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C185" s="11" t="s">
+      <c r="C185" s="26" t="s">
         <v>62</v>
       </c>
       <c r="D185" s="12">
@@ -6366,7 +6353,7 @@
       <c r="E185" s="4">
         <v>1274200</v>
       </c>
-      <c r="F185" s="29" t="s">
+      <c r="F185" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G185" s="12">
@@ -6383,8 +6370,8 @@
       <c r="B186" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C186" s="11" t="s">
-        <v>131</v>
+      <c r="C186" s="26" t="s">
+        <v>132</v>
       </c>
       <c r="D186" s="12">
         <v>46018</v>
@@ -6392,7 +6379,7 @@
       <c r="E186" s="4">
         <v>226000</v>
       </c>
-      <c r="F186" s="29" t="s">
+      <c r="F186" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G186" s="12">
@@ -6409,7 +6396,7 @@
       <c r="B187" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C187" s="11" t="s">
+      <c r="C187" s="26" t="s">
         <v>63</v>
       </c>
       <c r="D187" s="12">
@@ -6418,7 +6405,7 @@
       <c r="E187" s="4">
         <v>594500</v>
       </c>
-      <c r="F187" s="29" t="s">
+      <c r="F187" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G187" s="12">
@@ -6428,7 +6415,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="11" t="s">
         <v>0</v>
       </c>
@@ -6454,7 +6441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="11" t="s">
         <v>1</v>
       </c>
@@ -6480,7 +6467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="11" t="s">
         <v>33</v>
       </c>
@@ -6506,7 +6493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="11" t="s">
         <v>29</v>
       </c>
@@ -6539,7 +6526,7 @@
       <c r="B192" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C192" s="11" t="s">
+      <c r="C192" s="26" t="s">
         <v>64</v>
       </c>
       <c r="D192" s="12">
@@ -6548,7 +6535,7 @@
       <c r="E192" s="4">
         <v>1578194</v>
       </c>
-      <c r="F192" s="29" t="s">
+      <c r="F192" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G192" s="12">
@@ -6565,7 +6552,7 @@
       <c r="B193" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C193" s="11" t="s">
+      <c r="C193" s="26" t="s">
         <v>65</v>
       </c>
       <c r="D193" s="12">
@@ -6574,7 +6561,7 @@
       <c r="E193" s="4">
         <v>1076390</v>
       </c>
-      <c r="F193" s="29" t="s">
+      <c r="F193" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G193" s="12">
@@ -6584,7 +6571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="11" t="s">
         <v>29</v>
       </c>
@@ -6610,7 +6597,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="11" t="s">
         <v>29</v>
       </c>
@@ -6644,7 +6631,7 @@
       <c r="B196" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C196" s="11" t="s">
+      <c r="C196" s="26" t="s">
         <v>66</v>
       </c>
       <c r="D196" s="12">
@@ -6653,7 +6640,7 @@
       <c r="E196" s="4">
         <v>1554500</v>
       </c>
-      <c r="F196" s="29" t="s">
+      <c r="F196" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G196" s="12">
@@ -6670,7 +6657,7 @@
       <c r="B197" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C197" s="11" t="s">
+      <c r="C197" s="26" t="s">
         <v>67</v>
       </c>
       <c r="D197" s="12">
@@ -6679,7 +6666,7 @@
       <c r="E197" s="4">
         <v>171900</v>
       </c>
-      <c r="F197" s="29" t="s">
+      <c r="F197" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G197" s="12">
@@ -6689,7 +6676,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="11" t="s">
         <v>29</v>
       </c>
@@ -6715,7 +6702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="11" t="s">
         <v>29</v>
       </c>
@@ -6741,7 +6728,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="11" t="s">
         <v>40</v>
       </c>
@@ -6774,7 +6761,7 @@
       <c r="B201" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C201" s="11" t="s">
+      <c r="C201" s="26" t="s">
         <v>69</v>
       </c>
       <c r="D201" s="12">
@@ -6783,7 +6770,7 @@
       <c r="E201" s="4">
         <v>987190</v>
       </c>
-      <c r="F201" s="29" t="s">
+      <c r="F201" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G201" s="12">
@@ -6800,7 +6787,7 @@
       <c r="B202" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C202" s="11" t="s">
+      <c r="C202" s="26" t="s">
         <v>70</v>
       </c>
       <c r="D202" s="12">
@@ -6809,7 +6796,7 @@
       <c r="E202" s="4">
         <v>87000</v>
       </c>
-      <c r="F202" s="29" t="s">
+      <c r="F202" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G202" s="12">
@@ -6826,7 +6813,7 @@
       <c r="B203" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C203" s="11" t="s">
+      <c r="C203" s="26" t="s">
         <v>71</v>
       </c>
       <c r="D203" s="12">
@@ -6835,7 +6822,7 @@
       <c r="E203" s="4">
         <v>1530000</v>
       </c>
-      <c r="F203" s="29" t="s">
+      <c r="F203" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G203" s="12">
@@ -6845,7 +6832,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="11" t="s">
         <v>27</v>
       </c>
@@ -6871,7 +6858,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="11" t="s">
         <v>26</v>
       </c>
@@ -6904,7 +6891,7 @@
       <c r="B206" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C206" s="11" t="s">
+      <c r="C206" s="26" t="s">
         <v>72</v>
       </c>
       <c r="D206" s="12">
@@ -6913,7 +6900,7 @@
       <c r="E206" s="4">
         <v>1479500</v>
       </c>
-      <c r="F206" s="28" t="s">
+      <c r="F206" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G206" s="12">
@@ -6923,7 +6910,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="11" t="s">
         <v>30</v>
       </c>
@@ -6956,7 +6943,7 @@
       <c r="B208" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C208" s="11" t="s">
+      <c r="C208" s="26" t="s">
         <v>73</v>
       </c>
       <c r="D208" s="12">
@@ -6965,7 +6952,7 @@
       <c r="E208" s="4">
         <v>1869720</v>
       </c>
-      <c r="F208" s="29" t="s">
+      <c r="F208" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G208" s="12">
@@ -6982,7 +6969,7 @@
       <c r="B209" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C209" s="11" t="s">
+      <c r="C209" s="26" t="s">
         <v>74</v>
       </c>
       <c r="D209" s="12">
@@ -6991,7 +6978,7 @@
       <c r="E209" s="4">
         <v>163500</v>
       </c>
-      <c r="F209" s="29" t="s">
+      <c r="F209" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G209" s="12">
@@ -7001,7 +6988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="11" t="s">
         <v>35</v>
       </c>
@@ -7027,7 +7014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="11" t="s">
         <v>0</v>
       </c>
@@ -7053,7 +7040,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="11" t="s">
         <v>1</v>
       </c>
@@ -7079,7 +7066,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="11" t="s">
         <v>33</v>
       </c>
@@ -7105,7 +7092,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="11" t="s">
         <v>75</v>
       </c>
@@ -7131,7 +7118,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="11" t="s">
         <v>76</v>
       </c>
@@ -7157,12 +7144,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C216" s="11" t="s">
         <v>68</v>
@@ -7190,7 +7177,7 @@
       <c r="B217" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C217" s="11" t="s">
+      <c r="C217" s="26" t="s">
         <v>77</v>
       </c>
       <c r="D217" s="12">
@@ -7199,7 +7186,7 @@
       <c r="E217" s="4">
         <v>540480</v>
       </c>
-      <c r="F217" s="29" t="s">
+      <c r="F217" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G217" s="12">
@@ -7216,7 +7203,7 @@
       <c r="B218" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C218" s="11" t="s">
+      <c r="C218" s="26" t="s">
         <v>78</v>
       </c>
       <c r="D218" s="12">
@@ -7225,7 +7212,7 @@
       <c r="E218" s="4">
         <v>460500</v>
       </c>
-      <c r="F218" s="28" t="s">
+      <c r="F218" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G218" s="12">
@@ -7242,7 +7229,7 @@
       <c r="B219" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C219" s="11" t="s">
+      <c r="C219" s="26" t="s">
         <v>79</v>
       </c>
       <c r="D219" s="12">
@@ -7251,7 +7238,7 @@
       <c r="E219" s="4">
         <v>754700</v>
       </c>
-      <c r="F219" s="28" t="s">
+      <c r="F219" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G219" s="12">
@@ -7268,7 +7255,7 @@
       <c r="B220" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C220" s="11" t="s">
+      <c r="C220" s="26" t="s">
         <v>80</v>
       </c>
       <c r="D220" s="12">
@@ -7277,7 +7264,7 @@
       <c r="E220" s="4">
         <v>1043800</v>
       </c>
-      <c r="F220" s="29" t="s">
+      <c r="F220" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G220" s="12">
@@ -7294,7 +7281,7 @@
       <c r="B221" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C221" s="11" t="s">
+      <c r="C221" s="26" t="s">
         <v>81</v>
       </c>
       <c r="D221" s="12">
@@ -7303,7 +7290,7 @@
       <c r="E221" s="4">
         <v>745850</v>
       </c>
-      <c r="F221" s="29" t="s">
+      <c r="F221" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G221" s="12">
@@ -7313,7 +7300,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="11" t="s">
         <v>29</v>
       </c>
@@ -7340,7 +7327,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="11" t="s">
         <v>29</v>
       </c>
@@ -7366,7 +7353,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="11" t="s">
         <v>29</v>
       </c>
@@ -7393,7 +7380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="11" t="s">
         <v>29</v>
       </c>
@@ -7419,7 +7406,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
         <v>29</v>
       </c>
@@ -7445,7 +7432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>29</v>
       </c>
@@ -7479,7 +7466,7 @@
       <c r="B228" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C228" s="11" t="s">
+      <c r="C228" s="26" t="s">
         <v>82</v>
       </c>
       <c r="D228" s="12">
@@ -7488,7 +7475,7 @@
       <c r="E228" s="4">
         <v>923900</v>
       </c>
-      <c r="F228" s="29" t="s">
+      <c r="F228" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G228" s="12">
@@ -7499,7 +7486,7 @@
       </c>
       <c r="I228" s="1"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="11" t="s">
         <v>104</v>
       </c>
@@ -7533,7 +7520,7 @@
       <c r="B230" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C230" s="11" t="s">
+      <c r="C230" s="26" t="s">
         <v>83</v>
       </c>
       <c r="D230" s="12">
@@ -7542,7 +7529,7 @@
       <c r="E230" s="4">
         <v>1255960</v>
       </c>
-      <c r="F230" s="29" t="s">
+      <c r="F230" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G230" s="12">
@@ -7558,10 +7545,10 @@
         <v>14</v>
       </c>
       <c r="B231" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C231" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D231" s="12">
         <v>46051</v>
@@ -7576,7 +7563,7 @@
       </c>
       <c r="I231" s="1"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="11" t="s">
         <v>0</v>
       </c>
@@ -7603,7 +7590,7 @@
       </c>
       <c r="I232" s="1"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="11" t="s">
         <v>1</v>
       </c>
@@ -7619,7 +7606,7 @@
       <c r="E233" s="4">
         <v>1500000</v>
       </c>
-      <c r="F233" s="6" t="s">
+      <c r="F233" s="31" t="s">
         <v>3</v>
       </c>
       <c r="G233" s="12">
@@ -7629,7 +7616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="11" t="s">
         <v>111</v>
       </c>
@@ -7655,7 +7642,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="11" t="s">
         <v>112</v>
       </c>
@@ -7681,12 +7668,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B236" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C236" s="11" t="s">
         <v>68</v>
@@ -7714,7 +7701,7 @@
       <c r="B237" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C237" s="11" t="s">
+      <c r="C237" s="26" t="s">
         <v>84</v>
       </c>
       <c r="D237" s="12">
@@ -7723,7 +7710,7 @@
       <c r="E237" s="4">
         <v>775840</v>
       </c>
-      <c r="F237" s="29" t="s">
+      <c r="F237" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G237" s="12">
@@ -7740,7 +7727,7 @@
       <c r="B238" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C238" s="11" t="s">
+      <c r="C238" s="26" t="s">
         <v>85</v>
       </c>
       <c r="D238" s="12">
@@ -7749,7 +7736,7 @@
       <c r="E238" s="4">
         <v>136300</v>
       </c>
-      <c r="F238" s="29" t="s">
+      <c r="F238" s="30" t="s">
         <v>3</v>
       </c>
       <c r="G238" s="12">
@@ -7759,7 +7746,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="11" t="s">
         <v>39</v>
       </c>
@@ -7785,7 +7772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="11" t="s">
         <v>32</v>
       </c>
@@ -7811,7 +7798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="11" t="s">
         <v>32</v>
       </c>
@@ -7837,7 +7824,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="11" t="s">
         <v>40</v>
       </c>
@@ -7870,7 +7857,7 @@
       <c r="B243" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C243" s="11" t="s">
+      <c r="C243" s="26" t="s">
         <v>87</v>
       </c>
       <c r="D243" s="12">
@@ -7879,7 +7866,7 @@
       <c r="E243" s="4">
         <v>1143700</v>
       </c>
-      <c r="F243" s="28" t="s">
+      <c r="F243" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G243" s="12">
@@ -7896,7 +7883,7 @@
       <c r="B244" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C244" s="11" t="s">
+      <c r="C244" s="26" t="s">
         <v>88</v>
       </c>
       <c r="D244" s="12">
@@ -7905,7 +7892,7 @@
       <c r="E244" s="4">
         <v>39900</v>
       </c>
-      <c r="F244" s="28" t="s">
+      <c r="F244" s="29" t="s">
         <v>2</v>
       </c>
       <c r="G244" s="12">
@@ -7915,15 +7902,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C245" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D245" s="12">
         <v>46059</v>
@@ -7941,15 +7928,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="11" t="s">
         <v>116</v>
       </c>
       <c r="B246" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C246" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D246" s="12">
         <v>46059</v>
@@ -7967,15 +7954,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B247" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C247" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="B247" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C247" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="D247" s="12">
         <v>46059</v>
@@ -7991,15 +7978,15 @@
       </c>
       <c r="H247" s="11"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="11" t="s">
         <v>116</v>
       </c>
       <c r="B248" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C248" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D248" s="12">
         <v>46059</v>
@@ -8015,15 +8002,15 @@
       </c>
       <c r="H248" s="11"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C249" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D249" s="12">
         <v>46060</v>
@@ -8041,7 +8028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="11" t="s">
         <v>30</v>
       </c>
@@ -8072,10 +8059,10 @@
         <v>14</v>
       </c>
       <c r="B251" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C251" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D251" s="12">
         <v>46060</v>
@@ -8098,10 +8085,10 @@
         <v>14</v>
       </c>
       <c r="B252" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C252" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D252" s="12">
         <v>46060</v>
@@ -8126,7 +8113,7 @@
       <c r="B253" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C253" s="11" t="s">
+      <c r="C253" s="26" t="s">
         <v>89</v>
       </c>
       <c r="D253" s="12">
@@ -8150,10 +8137,10 @@
         <v>14</v>
       </c>
       <c r="B254" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C254" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D254" s="12">
         <v>46060</v>
@@ -8174,7 +8161,7 @@
       <c r="B255" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C255" s="11" t="s">
+      <c r="C255" s="26" t="s">
         <v>92</v>
       </c>
       <c r="D255" s="12">
@@ -8193,7 +8180,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="11" t="s">
         <v>27</v>
       </c>
@@ -8219,7 +8206,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="11" t="s">
         <v>26</v>
       </c>
@@ -8252,7 +8239,7 @@
       <c r="B258" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C258" s="11" t="s">
+      <c r="C258" s="26" t="s">
         <v>93</v>
       </c>
       <c r="D258" s="12">
@@ -8278,7 +8265,7 @@
       <c r="B259" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C259" s="11" t="s">
+      <c r="C259" s="26" t="s">
         <v>94</v>
       </c>
       <c r="D259" s="12">
@@ -8304,7 +8291,7 @@
       <c r="B260" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C260" s="11" t="s">
+      <c r="C260" s="26" t="s">
         <v>95</v>
       </c>
       <c r="D260" s="12">
@@ -8324,7 +8311,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="11" t="s">
         <v>35</v>
       </c>
@@ -8350,7 +8337,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="11" t="s">
         <v>0</v>
       </c>
@@ -8377,7 +8364,7 @@
       </c>
       <c r="I262" s="1"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="11" t="s">
         <v>1</v>
       </c>
@@ -8403,7 +8390,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="11" t="s">
         <v>112</v>
       </c>
@@ -8429,7 +8416,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="11" t="s">
         <v>111</v>
       </c>
@@ -8455,12 +8442,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B266" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C266" s="11" t="s">
         <v>86</v>
@@ -8488,7 +8475,7 @@
       <c r="B267" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C267" s="11" t="s">
+      <c r="C267" s="26" t="s">
         <v>96</v>
       </c>
       <c r="D267" s="12">
@@ -8514,7 +8501,7 @@
       <c r="B268" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C268" s="11" t="s">
+      <c r="C268" s="26" t="s">
         <v>97</v>
       </c>
       <c r="D268" s="12">
@@ -8540,7 +8527,7 @@
       <c r="B269" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C269" s="11" t="s">
+      <c r="C269" s="26" t="s">
         <v>98</v>
       </c>
       <c r="D269" s="12">
@@ -8566,7 +8553,7 @@
       <c r="B270" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C270" s="11" t="s">
+      <c r="C270" s="26" t="s">
         <v>99</v>
       </c>
       <c r="D270" s="12">
@@ -8585,7 +8572,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="11" t="s">
         <v>29</v>
       </c>
@@ -8598,7 +8585,7 @@
       <c r="D271" s="12">
         <v>46076</v>
       </c>
-      <c r="E271" s="26">
+      <c r="E271" s="27">
         <f>(432417*0.88)+82158</f>
         <v>462684.96</v>
       </c>
@@ -8612,7 +8599,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="11" t="s">
         <v>29</v>
       </c>
@@ -8645,7 +8632,7 @@
       <c r="B273" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C273" s="11" t="s">
+      <c r="C273" s="26" t="s">
         <v>100</v>
       </c>
       <c r="D273" s="12">
@@ -8671,7 +8658,7 @@
       <c r="B274" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C274" s="11" t="s">
+      <c r="C274" s="26" t="s">
         <v>102</v>
       </c>
       <c r="D274" s="12">
@@ -8697,7 +8684,7 @@
       <c r="B275" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C275" s="11" t="s">
+      <c r="C275" s="26" t="s">
         <v>101</v>
       </c>
       <c r="D275" s="12">
@@ -8723,7 +8710,7 @@
       <c r="B276" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C276" s="11" t="s">
+      <c r="C276" s="26" t="s">
         <v>103</v>
       </c>
       <c r="D276" s="12">
@@ -8749,8 +8736,8 @@
       <c r="B277" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C277" s="11" t="s">
-        <v>159</v>
+      <c r="C277" s="26" t="s">
+        <v>160</v>
       </c>
       <c r="D277" s="12">
         <v>46080</v>
@@ -8768,15 +8755,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="11" t="s">
         <v>116</v>
       </c>
       <c r="B278" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C278" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D278" s="12">
         <v>46081</v>
@@ -8795,15 +8782,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C279" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D279" s="12">
         <v>46081</v>
@@ -8822,15 +8809,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B280" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C280" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D280" s="12">
         <v>46081</v>
@@ -8849,7 +8836,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="11" t="s">
         <v>0</v>
       </c>
@@ -8875,7 +8862,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="11" t="s">
         <v>1</v>
       </c>
@@ -8901,7 +8888,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="11" t="s">
         <v>111</v>
       </c>
@@ -8927,7 +8914,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
         <v>112</v>
       </c>
@@ -8953,12 +8940,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B285" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C285" s="11" t="s">
         <v>86</v>
@@ -8969,7 +8956,7 @@
       <c r="E285" s="4">
         <v>500000</v>
       </c>
-      <c r="F285" s="6" t="s">
+      <c r="F285" s="31" t="s">
         <v>3</v>
       </c>
       <c r="G285" s="12">
@@ -8986,7 +8973,7 @@
       <c r="B286" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C286" s="11" t="s">
+      <c r="C286" s="26" t="s">
         <v>105</v>
       </c>
       <c r="D286" s="12">
@@ -9005,7 +8992,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="11" t="s">
         <v>32</v>
       </c>
@@ -9038,7 +9025,7 @@
       <c r="B288" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C288" s="11" t="s">
+      <c r="C288" s="26" t="s">
         <v>108</v>
       </c>
       <c r="D288" s="12">
@@ -9064,7 +9051,7 @@
       <c r="B289" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C289" s="11" t="s">
+      <c r="C289" s="26" t="s">
         <v>109</v>
       </c>
       <c r="D289" s="12">
@@ -9083,7 +9070,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="11" t="s">
         <v>40</v>
       </c>
@@ -9116,7 +9103,7 @@
       <c r="B291" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C291" s="11" t="s">
+      <c r="C291" s="26" t="s">
         <v>107</v>
       </c>
       <c r="D291" s="12">
@@ -9142,7 +9129,7 @@
       <c r="B292" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C292" s="11" t="s">
+      <c r="C292" s="26" t="s">
         <v>106</v>
       </c>
       <c r="D292" s="12">
@@ -9168,7 +9155,7 @@
       <c r="B293" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C293" s="11" t="s">
+      <c r="C293" s="26" t="s">
         <v>110</v>
       </c>
       <c r="D293" s="12">
@@ -9194,7 +9181,7 @@
       <c r="B294" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C294" s="11" t="s">
+      <c r="C294" s="26" t="s">
         <v>113</v>
       </c>
       <c r="D294" s="12">
@@ -9220,7 +9207,7 @@
       <c r="B295" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C295" s="11" t="s">
+      <c r="C295" s="26" t="s">
         <v>114</v>
       </c>
       <c r="D295" s="12">
@@ -9246,7 +9233,7 @@
       <c r="B296" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C296" s="11" t="s">
+      <c r="C296" s="26" t="s">
         <v>115</v>
       </c>
       <c r="D296" s="12">
@@ -9265,7 +9252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="11" t="s">
         <v>27</v>
       </c>
@@ -9298,8 +9285,8 @@
       <c r="B298" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C298" s="11" t="s">
-        <v>124</v>
+      <c r="C298" s="26" t="s">
+        <v>125</v>
       </c>
       <c r="D298" s="12">
         <v>46092</v>
@@ -9317,7 +9304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="11" t="s">
         <v>26</v>
       </c>
@@ -9343,7 +9330,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="11" t="s">
         <v>30</v>
       </c>
@@ -9376,8 +9363,8 @@
       <c r="B301" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C301" s="11" t="s">
-        <v>125</v>
+      <c r="C301" s="26" t="s">
+        <v>126</v>
       </c>
       <c r="D301" s="12">
         <v>46093</v>
@@ -9395,7 +9382,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="11" t="s">
         <v>29</v>
       </c>
@@ -9408,7 +9395,7 @@
       <c r="D302" s="12">
         <v>46094</v>
       </c>
-      <c r="E302" s="26">
+      <c r="E302" s="27">
         <f>116753*0.88</f>
         <v>102742.64</v>
       </c>
@@ -9422,7 +9409,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="11" t="s">
         <v>29</v>
       </c>
@@ -9448,7 +9435,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="11" t="s">
         <v>29</v>
       </c>
@@ -9474,7 +9461,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="11" t="s">
         <v>29</v>
       </c>
@@ -9487,7 +9474,7 @@
       <c r="D305" s="12">
         <v>46095</v>
       </c>
-      <c r="E305" s="26">
+      <c r="E305" s="27">
         <f>174968*0.88</f>
         <v>153971.84</v>
       </c>
@@ -9508,8 +9495,8 @@
       <c r="B306" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C306" s="11" t="s">
-        <v>126</v>
+      <c r="C306" s="26" t="s">
+        <v>127</v>
       </c>
       <c r="D306" s="12">
         <v>46095</v>
@@ -9527,7 +9514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="11" t="s">
         <v>35</v>
       </c>
@@ -9553,7 +9540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="11" t="s">
         <v>0</v>
       </c>
@@ -9579,7 +9566,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="11" t="s">
         <v>1</v>
       </c>
@@ -9605,7 +9592,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="11" t="s">
         <v>112</v>
       </c>
@@ -9631,7 +9618,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="11" t="s">
         <v>111</v>
       </c>
@@ -9657,12 +9644,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B312" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C312" s="11" t="s">
         <v>91</v>
@@ -9690,8 +9677,8 @@
       <c r="B313" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C313" s="11" t="s">
-        <v>139</v>
+      <c r="C313" s="26" t="s">
+        <v>140</v>
       </c>
       <c r="D313" s="12">
         <v>46096</v>
@@ -9716,8 +9703,8 @@
       <c r="B314" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C314" s="11" t="s">
-        <v>133</v>
+      <c r="C314" s="26" t="s">
+        <v>134</v>
       </c>
       <c r="D314" s="12">
         <v>46101</v>
@@ -9742,8 +9729,8 @@
       <c r="B315" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C315" s="11" t="s">
-        <v>132</v>
+      <c r="C315" s="26" t="s">
+        <v>133</v>
       </c>
       <c r="D315" s="12">
         <v>46102</v>
@@ -9761,7 +9748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="11" t="s">
         <v>29</v>
       </c>
@@ -9774,7 +9761,7 @@
       <c r="D316" s="12">
         <v>46104</v>
       </c>
-      <c r="E316" s="27">
+      <c r="E316" s="28">
         <v>905287</v>
       </c>
       <c r="F316" s="11" t="s">
@@ -9787,7 +9774,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="11" t="s">
         <v>29</v>
       </c>
@@ -9814,7 +9801,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="11" t="s">
         <v>29</v>
       </c>
@@ -9827,7 +9814,7 @@
       <c r="D318" s="12">
         <v>46104</v>
       </c>
-      <c r="E318" s="27">
+      <c r="E318" s="28">
         <v>714340</v>
       </c>
       <c r="F318" s="11" t="s">
@@ -9840,7 +9827,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="11" t="s">
         <v>29</v>
       </c>
@@ -9853,7 +9840,7 @@
       <c r="D319" s="12">
         <v>46104</v>
       </c>
-      <c r="E319" s="27">
+      <c r="E319" s="28">
         <v>99953</v>
       </c>
       <c r="F319" s="11" t="s">
@@ -9873,8 +9860,8 @@
       <c r="B320" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C320" s="11" t="s">
-        <v>136</v>
+      <c r="C320" s="26" t="s">
+        <v>137</v>
       </c>
       <c r="D320" s="12">
         <v>46104</v>
@@ -9899,8 +9886,8 @@
       <c r="B321" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C321" s="11" t="s">
-        <v>135</v>
+      <c r="C321" s="26" t="s">
+        <v>136</v>
       </c>
       <c r="D321" s="12">
         <v>46104</v>
@@ -9918,7 +9905,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="11" t="s">
         <v>29</v>
       </c>
@@ -9931,7 +9918,7 @@
       <c r="D322" s="12">
         <v>46106</v>
       </c>
-      <c r="E322" s="27">
+      <c r="E322" s="28">
         <v>120000</v>
       </c>
       <c r="F322" s="11" t="s">
@@ -9951,13 +9938,13 @@
       <c r="B323" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C323" s="11" t="s">
-        <v>137</v>
+      <c r="C323" s="26" t="s">
+        <v>138</v>
       </c>
       <c r="D323" s="12">
         <v>46106</v>
       </c>
-      <c r="E323" s="27">
+      <c r="E323" s="28">
         <v>1069881</v>
       </c>
       <c r="F323" s="11" t="s">
@@ -9977,13 +9964,13 @@
       <c r="B324" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C324" s="11" t="s">
-        <v>138</v>
+      <c r="C324" s="26" t="s">
+        <v>139</v>
       </c>
       <c r="D324" s="12">
         <v>46108</v>
       </c>
-      <c r="E324" s="27">
+      <c r="E324" s="28">
         <v>1109600</v>
       </c>
       <c r="F324" s="11" t="s">
@@ -9996,7 +9983,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="11" t="s">
         <v>32</v>
       </c>
@@ -10029,13 +10016,13 @@
       <c r="B326" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C326" s="11" t="s">
-        <v>140</v>
+      <c r="C326" s="26" t="s">
+        <v>141</v>
       </c>
       <c r="D326" s="12">
         <v>46110</v>
       </c>
-      <c r="E326" s="27">
+      <c r="E326" s="28">
         <v>1375476</v>
       </c>
       <c r="F326" s="11" t="s">
@@ -10056,12 +10043,12 @@
         <v>15</v>
       </c>
       <c r="C327" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D327" s="12">
         <v>46110</v>
       </c>
-      <c r="E327" s="27">
+      <c r="E327" s="28">
         <v>1049633</v>
       </c>
       <c r="F327" s="11" t="s">
@@ -10074,7 +10061,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="11" t="s">
         <v>104</v>
       </c>
@@ -10087,7 +10074,7 @@
       <c r="D328" s="12">
         <v>46111</v>
       </c>
-      <c r="E328" s="27">
+      <c r="E328" s="28">
         <v>403520</v>
       </c>
       <c r="F328" s="11" t="s">
@@ -10098,7 +10085,7 @@
       </c>
       <c r="H328" s="11"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="11" t="s">
         <v>1</v>
       </c>
@@ -10124,7 +10111,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="11" t="s">
         <v>0</v>
       </c>
@@ -10150,7 +10137,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="11" t="s">
         <v>111</v>
       </c>
@@ -10176,7 +10163,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="11" t="s">
         <v>112</v>
       </c>
@@ -10202,12 +10189,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B333" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C333" s="11" t="s">
         <v>91</v>
@@ -10219,7 +10206,7 @@
         <v>500000</v>
       </c>
       <c r="F333" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G333" s="12">
         <v>46118</v>
@@ -10228,15 +10215,15 @@
         <v>119</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="11" t="s">
         <v>116</v>
       </c>
       <c r="B334" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C334" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D334" s="12">
         <v>46111</v>
@@ -10251,15 +10238,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C335" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D335" s="12">
         <v>46111</v>
@@ -10274,15 +10261,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C336" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D336" s="12">
         <v>46111</v>
@@ -10305,12 +10292,12 @@
         <v>15</v>
       </c>
       <c r="C337" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D337" s="12">
         <v>46113</v>
       </c>
-      <c r="E337" s="27">
+      <c r="E337" s="28">
         <v>1138600</v>
       </c>
       <c r="F337" s="11" t="s">
@@ -10323,7 +10310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="11" t="s">
         <v>29</v>
       </c>
@@ -10336,7 +10323,7 @@
       <c r="D338" s="12">
         <v>46114</v>
       </c>
-      <c r="E338" s="27">
+      <c r="E338" s="28">
         <v>2360930</v>
       </c>
       <c r="F338" s="11" t="s">
@@ -10349,7 +10336,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="11" t="s">
         <v>40</v>
       </c>
@@ -10375,12 +10362,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C340" s="11" t="s">
         <v>91</v>
@@ -10388,7 +10375,7 @@
       <c r="D340" s="12">
         <v>46117</v>
       </c>
-      <c r="E340" s="27">
+      <c r="E340" s="28">
         <v>248163</v>
       </c>
       <c r="F340" s="11" t="s">
@@ -10401,12 +10388,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B341" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C341" s="11" t="s">
         <v>91</v>
@@ -10414,7 +10401,7 @@
       <c r="D341" s="12">
         <v>46117</v>
       </c>
-      <c r="E341" s="27">
+      <c r="E341" s="28">
         <v>72665</v>
       </c>
       <c r="F341" s="11" t="s">
@@ -10435,12 +10422,12 @@
         <v>15</v>
       </c>
       <c r="C342" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D342" s="12">
         <v>46117</v>
       </c>
-      <c r="E342" s="27">
+      <c r="E342" s="28">
         <v>1226275</v>
       </c>
       <c r="F342" s="11" t="s">
@@ -10461,12 +10448,12 @@
         <v>15</v>
       </c>
       <c r="C343" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D343" s="12">
         <v>46120</v>
       </c>
-      <c r="E343" s="27">
+      <c r="E343" s="28">
         <v>1274025</v>
       </c>
       <c r="F343" s="11" t="s">
@@ -10479,7 +10466,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="11" t="s">
         <v>27</v>
       </c>
@@ -10505,7 +10492,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="11" t="s">
         <v>26</v>
       </c>
@@ -10531,7 +10518,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="11" t="s">
         <v>30</v>
       </c>
@@ -10565,12 +10552,12 @@
         <v>15</v>
       </c>
       <c r="C347" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D347" s="12">
         <v>46123</v>
       </c>
-      <c r="E347" s="27">
+      <c r="E347" s="28">
         <v>1262190</v>
       </c>
       <c r="F347" s="11" t="s">
@@ -10583,7 +10570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="11" t="s">
         <v>30</v>
       </c>
@@ -10609,7 +10596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="11" t="s">
         <v>35</v>
       </c>
@@ -10635,7 +10622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="11" t="s">
         <v>0</v>
       </c>
@@ -10661,7 +10648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="11" t="s">
         <v>1</v>
       </c>
@@ -10687,7 +10674,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="11" t="s">
         <v>112</v>
       </c>
@@ -10713,9 +10700,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B353" s="11" t="s">
         <v>34</v>
@@ -10739,12 +10726,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C354" s="11" t="s">
         <v>16</v>
@@ -10773,12 +10760,12 @@
         <v>15</v>
       </c>
       <c r="C355" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D355" s="12">
         <v>46127</v>
       </c>
-      <c r="E355" s="27">
+      <c r="E355" s="28">
         <v>1040450</v>
       </c>
       <c r="F355" s="11" t="s">
@@ -10799,12 +10786,12 @@
         <v>15</v>
       </c>
       <c r="C356" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D356" s="12">
         <v>46130</v>
       </c>
-      <c r="E356" s="27">
+      <c r="E356" s="28">
         <v>809570</v>
       </c>
       <c r="F356" s="11" t="s">
@@ -10825,12 +10812,12 @@
         <v>15</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D357" s="12">
         <v>46132</v>
       </c>
-      <c r="E357" s="27">
+      <c r="E357" s="28">
         <v>746910</v>
       </c>
       <c r="F357" s="11" t="s">
@@ -10851,12 +10838,12 @@
         <v>15</v>
       </c>
       <c r="C358" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D358" s="12">
         <v>46136</v>
       </c>
-      <c r="E358" s="27">
+      <c r="E358" s="28">
         <v>1052400</v>
       </c>
       <c r="F358" s="11" t="s">
@@ -10869,7 +10856,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="11" t="s">
         <v>32</v>
       </c>
@@ -10903,12 +10890,12 @@
         <v>15</v>
       </c>
       <c r="C360" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D360" s="12">
         <v>46138</v>
       </c>
-      <c r="E360" s="27">
+      <c r="E360" s="28">
         <v>1010000</v>
       </c>
       <c r="F360" s="11" t="s">
@@ -10929,12 +10916,12 @@
         <v>15</v>
       </c>
       <c r="C361" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D361" s="12">
         <v>46141</v>
       </c>
-      <c r="E361" s="27">
+      <c r="E361" s="28">
         <v>1189830</v>
       </c>
       <c r="F361" s="11" t="s">
@@ -10947,7 +10934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="11" t="s">
         <v>0</v>
       </c>
@@ -10973,7 +10960,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="11" t="s">
         <v>1</v>
       </c>
@@ -10999,9 +10986,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B364" s="11" t="s">
         <v>34</v>
@@ -11025,7 +11012,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="11" t="s">
         <v>112</v>
       </c>
@@ -11051,12 +11038,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B366" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C366" s="11" t="s">
         <v>16</v>
@@ -11077,12 +11064,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B367" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C367" s="11" t="s">
         <v>16</v>
@@ -11101,12 +11088,12 @@
       </c>
       <c r="H367" s="11"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B368" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C368" s="11" t="s">
         <v>16</v>
@@ -11125,15 +11112,15 @@
       </c>
       <c r="H368" s="11"/>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="11" t="s">
         <v>116</v>
       </c>
       <c r="B369" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C369" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D369" s="12">
         <v>46142</v>
@@ -11148,15 +11135,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B370" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C370" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D370" s="12">
         <v>46142</v>
@@ -11170,15 +11157,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B371" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C371" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D371" s="12">
         <v>46142</v>
@@ -11197,15 +11184,15 @@
         <v>14</v>
       </c>
       <c r="B372" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C372" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D372" s="12">
         <v>46143</v>
       </c>
-      <c r="E372" s="27">
+      <c r="E372" s="28">
         <v>1499230</v>
       </c>
       <c r="F372" s="11" t="s">
@@ -11226,12 +11213,12 @@
         <v>15</v>
       </c>
       <c r="C373" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D373" s="12">
         <v>46143</v>
       </c>
-      <c r="E373" s="27">
+      <c r="E373" s="28">
         <v>200800</v>
       </c>
       <c r="F373" s="11" t="s">
@@ -11244,7 +11231,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="11" t="s">
         <v>40</v>
       </c>
@@ -11270,7 +11257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="11" t="s">
         <v>29</v>
       </c>
@@ -11296,7 +11283,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="11" t="s">
         <v>29</v>
       </c>
@@ -11330,12 +11317,12 @@
         <v>15</v>
       </c>
       <c r="C377" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D377" s="12">
         <v>46148</v>
       </c>
-      <c r="E377" s="27">
+      <c r="E377" s="28">
         <v>1194230</v>
       </c>
       <c r="F377" s="11" t="s">
@@ -11348,7 +11335,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="11" t="s">
         <v>29</v>
       </c>
@@ -11361,7 +11348,7 @@
       <c r="D378" s="12">
         <v>46149</v>
       </c>
-      <c r="E378" s="27">
+      <c r="E378" s="28">
         <v>151767</v>
       </c>
       <c r="F378" s="11" t="s">
@@ -11374,7 +11361,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="11" t="s">
         <v>29</v>
       </c>
@@ -11400,7 +11387,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="11" t="s">
         <v>29</v>
       </c>
@@ -11427,7 +11414,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="11" t="s">
         <v>29</v>
       </c>
@@ -11461,7 +11448,7 @@
         <v>15</v>
       </c>
       <c r="C382" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D382" s="12">
         <v>46149</v>
@@ -11487,16 +11474,16 @@
         <v>15</v>
       </c>
       <c r="C383" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D383" s="12">
         <v>46151</v>
       </c>
-      <c r="E383" s="27">
+      <c r="E383" s="28">
         <v>869200</v>
       </c>
       <c r="F383" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G383" s="12">
         <v>46208</v>
@@ -11505,7 +11492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="11" t="s">
         <v>27</v>
       </c>
@@ -11531,7 +11518,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="11" t="s">
         <v>30</v>
       </c>
@@ -11566,12 +11553,12 @@
         <v>15</v>
       </c>
       <c r="C386" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D386" s="12">
         <v>46155</v>
       </c>
-      <c r="E386" s="27">
+      <c r="E386" s="28">
         <v>827854</v>
       </c>
       <c r="F386" s="11" t="s">
@@ -11584,7 +11571,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="11" t="s">
         <v>26</v>
       </c>
@@ -11610,12 +11597,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B388" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C388" s="11" t="s">
         <v>17</v>
@@ -11636,7 +11623,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="11" t="s">
         <v>35</v>
       </c>
@@ -11662,7 +11649,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="11" t="s">
         <v>0</v>
       </c>
@@ -11688,7 +11675,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="11" t="s">
         <v>1</v>
       </c>
@@ -11714,7 +11701,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="11" t="s">
         <v>112</v>
       </c>
@@ -11740,9 +11727,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B393" s="11" t="s">
         <v>34</v>
@@ -11774,12 +11761,12 @@
         <v>15</v>
       </c>
       <c r="C394" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D394" s="12">
         <v>46157</v>
       </c>
-      <c r="E394" s="27">
+      <c r="E394" s="28">
         <v>1067550</v>
       </c>
       <c r="F394" s="11" t="s">
@@ -11800,12 +11787,12 @@
         <v>15</v>
       </c>
       <c r="C395" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D395" s="12">
         <v>46158</v>
       </c>
-      <c r="E395" s="27">
+      <c r="E395" s="28">
         <v>91600</v>
       </c>
       <c r="F395" s="11" t="s">
@@ -11818,7 +11805,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="11" t="s">
         <v>32</v>
       </c>
@@ -11852,12 +11839,12 @@
         <v>15</v>
       </c>
       <c r="C397" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D397" s="12">
         <v>46159</v>
       </c>
-      <c r="E397" s="27">
+      <c r="E397" s="28">
         <v>570500</v>
       </c>
       <c r="F397" s="11" t="s">
@@ -11878,12 +11865,12 @@
         <v>15</v>
       </c>
       <c r="C398" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D398" s="12">
         <v>46160</v>
       </c>
-      <c r="E398" s="27">
+      <c r="E398" s="28">
         <v>98000</v>
       </c>
       <c r="F398" s="11" t="s">
@@ -11904,7 +11891,7 @@
         <v>15</v>
       </c>
       <c r="C399" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D399" s="12">
         <v>46162</v>
@@ -11930,7 +11917,7 @@
         <v>15</v>
       </c>
       <c r="C400" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D400" s="12">
         <v>46162</v>
@@ -11956,7 +11943,7 @@
         <v>15</v>
       </c>
       <c r="C401" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D401" s="12">
         <v>46165</v>
@@ -11982,7 +11969,7 @@
         <v>15</v>
       </c>
       <c r="C402" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D402" s="12">
         <v>46166</v>
@@ -12008,7 +11995,7 @@
         <v>15</v>
       </c>
       <c r="C403" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D403" s="12">
         <v>46166</v>
@@ -12026,7 +12013,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="11" t="s">
         <v>29</v>
       </c>
@@ -12052,7 +12039,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="11" t="s">
         <v>29</v>
       </c>
@@ -12078,7 +12065,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="406" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="11" t="s">
         <v>29</v>
       </c>
@@ -12112,7 +12099,7 @@
         <v>15</v>
       </c>
       <c r="C407" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D407" s="12">
         <v>46167</v>
@@ -12138,7 +12125,7 @@
         <v>15</v>
       </c>
       <c r="C408" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D408" s="12">
         <v>46169</v>
@@ -12156,7 +12143,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="409" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="11" t="s">
         <v>39</v>
       </c>
@@ -12182,7 +12169,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="410" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="11" t="s">
         <v>29</v>
       </c>
@@ -12216,7 +12203,7 @@
         <v>15</v>
       </c>
       <c r="C411" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D411" s="12">
         <v>46171</v>
@@ -12224,7 +12211,7 @@
       <c r="E411" s="4">
         <v>631950</v>
       </c>
-      <c r="F411" s="30" t="s">
+      <c r="F411" s="33" t="s">
         <v>2</v>
       </c>
       <c r="G411" s="12">
@@ -12242,7 +12229,7 @@
         <v>15</v>
       </c>
       <c r="C412" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D412" s="12">
         <v>46171</v>
@@ -12260,12 +12247,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="413" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B413" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C413" s="11" t="s">
         <v>17</v>
@@ -12276,7 +12263,7 @@
       <c r="E413" s="4">
         <v>500000</v>
       </c>
-      <c r="F413" s="30" t="s">
+      <c r="F413" s="33" t="s">
         <v>3</v>
       </c>
       <c r="G413" s="12">
@@ -12294,7 +12281,7 @@
         <v>15</v>
       </c>
       <c r="C414" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D414" s="12">
         <v>46174</v>
@@ -12320,7 +12307,7 @@
         <v>15</v>
       </c>
       <c r="C415" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D415" s="12">
         <v>46176</v>
@@ -12346,7 +12333,7 @@
         <v>15</v>
       </c>
       <c r="C416" s="11" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D416" s="12">
         <v>46177</v>
@@ -12364,7 +12351,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="417" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="11" t="s">
         <v>40</v>
       </c>
@@ -12398,7 +12385,7 @@
         <v>15</v>
       </c>
       <c r="C418" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D418" s="12">
         <v>46178</v>
@@ -12416,12 +12403,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="419" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B419" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C419" s="11" t="s">
         <v>19</v>
@@ -12429,7 +12416,7 @@
       <c r="D419" s="12">
         <v>46178</v>
       </c>
-      <c r="E419" s="27">
+      <c r="E419" s="28">
         <v>198600</v>
       </c>
       <c r="F419" s="11" t="s">
@@ -12442,12 +12429,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="420" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B420" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C420" s="11" t="s">
         <v>19</v>
@@ -12455,7 +12442,7 @@
       <c r="D420" s="12">
         <v>46178</v>
       </c>
-      <c r="E420" s="27">
+      <c r="E420" s="28">
         <v>182200</v>
       </c>
       <c r="F420" s="11" t="s">
@@ -12476,7 +12463,7 @@
         <v>15</v>
       </c>
       <c r="C421" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D421" s="12">
         <v>46179</v>
@@ -12494,7 +12481,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="422" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="11" t="s">
         <v>29</v>
       </c>
@@ -12521,7 +12508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="423" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="11" t="s">
         <v>29</v>
       </c>
@@ -12548,7 +12535,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="424" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="11" t="s">
         <v>32</v>
       </c>
@@ -12575,7 +12562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="425" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="11" t="s">
         <v>29</v>
       </c>
@@ -12610,7 +12597,7 @@
         <v>15</v>
       </c>
       <c r="C426" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D426" s="12">
         <v>46181</v>
@@ -12636,7 +12623,7 @@
         <v>15</v>
       </c>
       <c r="C427" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D427" s="12">
         <v>46183</v>
@@ -12662,7 +12649,7 @@
         <v>15</v>
       </c>
       <c r="C428" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D428" s="12">
         <v>46183</v>
@@ -12688,7 +12675,7 @@
         <v>15</v>
       </c>
       <c r="C429" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D429" s="12">
         <v>46183</v>
@@ -12706,7 +12693,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="430" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="11" t="s">
         <v>27</v>
       </c>
@@ -12732,7 +12719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="431" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="11" t="s">
         <v>30</v>
       </c>
@@ -12758,7 +12745,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="432" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="11" t="s">
         <v>30</v>
       </c>
@@ -12784,7 +12771,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="433" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="11" t="s">
         <v>26</v>
       </c>
@@ -12810,7 +12797,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="434" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="11" t="s">
         <v>14</v>
       </c>
@@ -12818,7 +12805,7 @@
         <v>15</v>
       </c>
       <c r="C434" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D434" s="12">
         <v>46186</v>
@@ -12836,7 +12823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="435" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="11" t="s">
         <v>14</v>
       </c>
@@ -12844,7 +12831,7 @@
         <v>15</v>
       </c>
       <c r="C435" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D435" s="12">
         <v>46186</v>
@@ -12862,7 +12849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="436" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="11" t="s">
         <v>14</v>
       </c>
@@ -12870,7 +12857,7 @@
         <v>15</v>
       </c>
       <c r="C436" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D436" s="12">
         <v>46187</v>
@@ -12888,7 +12875,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="437" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="11" t="s">
         <v>29</v>
       </c>
@@ -12915,7 +12902,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="438" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="11" t="s">
         <v>32</v>
       </c>
@@ -12942,12 +12929,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="439" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B439" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C439" s="11" t="s">
         <v>19</v>
@@ -12958,7 +12945,7 @@
       <c r="E439" s="4">
         <v>500000</v>
       </c>
-      <c r="F439" s="30" t="s">
+      <c r="F439" s="33" t="s">
         <v>3</v>
       </c>
       <c r="G439" s="12">
@@ -12968,7 +12955,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="440" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="11" t="s">
         <v>29</v>
       </c>
@@ -12995,7 +12982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="441" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="11" t="s">
         <v>0</v>
       </c>
@@ -13021,7 +13008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="442" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="11" t="s">
         <v>1</v>
       </c>
@@ -13047,7 +13034,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="443" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="11" t="s">
         <v>112</v>
       </c>
@@ -13073,9 +13060,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="444" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B444" s="11" t="s">
         <v>34</v>
@@ -13099,15 +13086,15 @@
         <v>119</v>
       </c>
     </row>
-    <row r="445" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B445" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C445" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D445" s="12">
         <v>46188</v>
@@ -13125,7 +13112,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="446" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="11" t="s">
         <v>112</v>
       </c>
@@ -13133,7 +13120,7 @@
         <v>34</v>
       </c>
       <c r="C446" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D446" s="12">
         <v>46188</v>
@@ -13151,7 +13138,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="447" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="11" t="s">
         <v>14</v>
       </c>
@@ -13159,7 +13146,7 @@
         <v>15</v>
       </c>
       <c r="C447" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D447" s="12">
         <v>46191</v>
@@ -13177,7 +13164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="448" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="11" t="s">
         <v>14</v>
       </c>
@@ -13185,7 +13172,7 @@
         <v>15</v>
       </c>
       <c r="C448" s="11" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D448" s="12">
         <v>46191</v>
@@ -13203,9 +13190,8 @@
       <c r="H448" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I448" s="31"/>
-    </row>
-    <row r="449" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="449" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="11" t="s">
         <v>29</v>
       </c>
@@ -13231,8 +13217,9 @@
       <c r="H449" s="11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="450" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I449" s="34"/>
+    </row>
+    <row r="450" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="11" t="s">
         <v>29</v>
       </c>
@@ -13258,15 +13245,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="451" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A451" s="30" t="s">
+    <row r="451" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A451" s="33" t="s">
         <v>14</v>
       </c>
       <c r="B451" s="11" t="s">
         <v>15</v>
       </c>
       <c r="C451" s="11" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D451" s="12">
         <v>46193</v>
@@ -13284,7 +13271,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="452" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="11" t="s">
         <v>14</v>
       </c>
@@ -13292,7 +13279,7 @@
         <v>15</v>
       </c>
       <c r="C452" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D452" s="12">
         <v>46194</v>
@@ -13310,7 +13297,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="453" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="11" t="s">
         <v>14</v>
       </c>
@@ -13318,7 +13305,7 @@
         <v>15</v>
       </c>
       <c r="C453" s="11" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D453" s="12">
         <v>46195</v>
@@ -13336,7 +13323,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="454" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="11" t="s">
         <v>14</v>
       </c>
@@ -13344,7 +13331,7 @@
         <v>15</v>
       </c>
       <c r="C454" s="11" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D454" s="12">
         <v>46195</v>
@@ -13362,7 +13349,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="455" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="11" t="s">
         <v>14</v>
       </c>
@@ -13370,7 +13357,7 @@
         <v>15</v>
       </c>
       <c r="C455" s="11" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D455" s="12">
         <v>46197</v>
@@ -13388,7 +13375,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="456" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="11" t="s">
         <v>39</v>
       </c>
@@ -13414,7 +13401,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="457" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="11" t="s">
         <v>14</v>
       </c>
@@ -13422,7 +13409,7 @@
         <v>15</v>
       </c>
       <c r="C457" s="11" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D457" s="12">
         <v>46198</v>
@@ -13440,7 +13427,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="458" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="11" t="s">
         <v>29</v>
       </c>
@@ -13467,7 +13454,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="459" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="11" t="s">
         <v>29</v>
       </c>
@@ -13493,7 +13480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="460" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="11" t="s">
         <v>29</v>
       </c>
@@ -13520,7 +13507,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="461" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="11" t="s">
         <v>14</v>
       </c>
@@ -13528,7 +13515,7 @@
         <v>15</v>
       </c>
       <c r="C461" s="11" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D461" s="12">
         <v>46200</v>
@@ -13546,7 +13533,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="462" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="11" t="s">
         <v>14</v>
       </c>
@@ -13554,7 +13541,7 @@
         <v>15</v>
       </c>
       <c r="C462" s="11" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="D462" s="12">
         <v>46201</v>
@@ -13572,7 +13559,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="463" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="11" t="s">
         <v>14</v>
       </c>
@@ -13580,7 +13567,7 @@
         <v>15</v>
       </c>
       <c r="C463" s="11" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D463" s="12">
         <v>46201</v>
@@ -13598,7 +13585,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="464" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="11" t="s">
         <v>0</v>
       </c>
@@ -13624,7 +13611,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="465" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="11" t="s">
         <v>1</v>
       </c>
@@ -13650,7 +13637,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="466" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="11" t="s">
         <v>33</v>
       </c>
@@ -13676,7 +13663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="467" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="11" t="s">
         <v>90</v>
       </c>
@@ -13702,12 +13689,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="468" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B468" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C468" s="11" t="s">
         <v>19</v>
@@ -13718,7 +13705,7 @@
       <c r="E468" s="4">
         <v>500000</v>
       </c>
-      <c r="F468" s="30" t="s">
+      <c r="F468" s="33" t="s">
         <v>3</v>
       </c>
       <c r="G468" s="12">
@@ -13736,7 +13723,7 @@
         <v>15</v>
       </c>
       <c r="C469" s="11" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D469" s="12">
         <v>46204</v>
@@ -13762,7 +13749,7 @@
         <v>15</v>
       </c>
       <c r="C470" s="11" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D470" s="12">
         <v>46207</v>
@@ -13788,7 +13775,7 @@
         <v>15</v>
       </c>
       <c r="C471" s="11" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D471" s="12">
         <v>46208</v>
@@ -13806,7 +13793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="472" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="11" t="s">
         <v>40</v>
       </c>
@@ -13839,8 +13826,8 @@
       <c r="B473" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C473" s="11" t="s">
-        <v>219</v>
+      <c r="C473" s="26" t="s">
+        <v>223</v>
       </c>
       <c r="D473" s="12">
         <v>46209</v>
@@ -13848,7 +13835,7 @@
       <c r="E473" s="4">
         <v>367500</v>
       </c>
-      <c r="F473" s="11" t="s">
+      <c r="F473" s="26" t="s">
         <v>3</v>
       </c>
       <c r="G473" s="12">
@@ -13866,7 +13853,7 @@
         <v>15</v>
       </c>
       <c r="C474" s="11" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D474" s="12">
         <v>46212</v>
@@ -13892,7 +13879,7 @@
         <v>15</v>
       </c>
       <c r="C475" s="11" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D475" s="12">
         <v>46212</v>
@@ -13910,7 +13897,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="476" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="11" t="s">
         <v>27</v>
       </c>
@@ -13936,7 +13923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="477" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="11" t="s">
         <v>30</v>
       </c>
@@ -13962,7 +13949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="478" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="11" t="s">
         <v>35</v>
       </c>
@@ -13996,7 +13983,7 @@
         <v>15</v>
       </c>
       <c r="C479" s="11" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D479" s="12">
         <v>46215</v>
@@ -14022,7 +14009,7 @@
         <v>15</v>
       </c>
       <c r="C480" s="11" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D480" s="12">
         <v>46215</v>
@@ -14040,7 +14027,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="481" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="11" t="s">
         <v>29</v>
       </c>
@@ -14067,7 +14054,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="482" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="11" t="s">
         <v>29</v>
       </c>
@@ -14093,7 +14080,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="483" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="11" t="s">
         <v>29</v>
       </c>
@@ -14119,7 +14106,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="484" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="11" t="s">
         <v>26</v>
       </c>
@@ -14145,7 +14132,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="485" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="11" t="s">
         <v>0</v>
       </c>
@@ -14171,7 +14158,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="486" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="11" t="s">
         <v>1</v>
       </c>
@@ -14191,7 +14178,7 @@
       <c r="G486" s="11"/>
       <c r="H486" s="11"/>
     </row>
-    <row r="487" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="11" t="s">
         <v>112</v>
       </c>
@@ -14217,12 +14204,12 @@
         <v>119</v>
       </c>
     </row>
-    <row r="488" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B488" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C488" s="11" t="s">
         <v>20</v>
@@ -14233,7 +14220,7 @@
       <c r="E488" s="4">
         <v>500000</v>
       </c>
-      <c r="F488" s="30" t="s">
+      <c r="F488" s="33" t="s">
         <v>3</v>
       </c>
       <c r="G488" s="12">
@@ -14243,9 +14230,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="489" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B489" s="11" t="s">
         <v>34</v>
@@ -14277,7 +14264,7 @@
         <v>15</v>
       </c>
       <c r="C490" s="11" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D490" s="12">
         <v>46219</v>
@@ -14295,7 +14282,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="491" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="11" t="s">
         <v>32</v>
       </c>
@@ -14330,7 +14317,7 @@
         <v>15</v>
       </c>
       <c r="C492" s="11" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D492" s="12">
         <v>46223</v>
@@ -14356,7 +14343,7 @@
         <v>15</v>
       </c>
       <c r="C493" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D493" s="12">
         <v>46226</v>
@@ -14364,8 +14351,12 @@
       <c r="E493" s="4">
         <v>906900</v>
       </c>
-      <c r="F493" s="11"/>
-      <c r="G493" s="11"/>
+      <c r="F493" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G493" s="12">
+        <v>46275</v>
+      </c>
       <c r="H493" s="11" t="s">
         <v>7</v>
       </c>
@@ -14378,7 +14369,7 @@
         <v>15</v>
       </c>
       <c r="C494" s="11" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D494" s="12">
         <v>46228</v>
@@ -14386,8 +14377,12 @@
       <c r="E494" s="4">
         <v>1289838</v>
       </c>
-      <c r="F494" s="11"/>
-      <c r="G494" s="11"/>
+      <c r="F494" s="33" t="s">
+        <v>3</v>
+      </c>
+      <c r="G494" s="12">
+        <v>46275</v>
+      </c>
       <c r="H494" s="11" t="s">
         <v>7</v>
       </c>
@@ -14399,8 +14394,8 @@
       <c r="B495" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C495" s="30" t="s">
-        <v>228</v>
+      <c r="C495" s="33" t="s">
+        <v>232</v>
       </c>
       <c r="D495" s="12">
         <v>46230</v>
@@ -14408,13 +14403,17 @@
       <c r="E495" s="4">
         <v>958920</v>
       </c>
-      <c r="F495" s="11"/>
-      <c r="G495" s="11"/>
+      <c r="F495" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G495" s="12">
+        <v>46286</v>
+      </c>
       <c r="H495" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="496" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="11" t="s">
         <v>0</v>
       </c>
@@ -14434,7 +14433,7 @@
       <c r="G496" s="11"/>
       <c r="H496" s="11"/>
     </row>
-    <row r="497" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="11" t="s">
         <v>1</v>
       </c>
@@ -14454,9 +14453,9 @@
       <c r="G497" s="11"/>
       <c r="H497" s="11"/>
     </row>
-    <row r="498" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="11" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B498" s="11" t="s">
         <v>34</v>
@@ -14478,9 +14477,9 @@
       </c>
       <c r="H498" s="11"/>
     </row>
-    <row r="499" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B499" s="11" t="s">
         <v>34</v>
@@ -14510,7 +14509,7 @@
         <v>15</v>
       </c>
       <c r="C500" s="11" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D500" s="12">
         <v>46233</v>
@@ -14518,18 +14517,22 @@
       <c r="E500" s="4">
         <v>533600</v>
       </c>
-      <c r="F500" s="11"/>
-      <c r="G500" s="11"/>
+      <c r="F500" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G500" s="12">
+        <v>46286</v>
+      </c>
       <c r="H500" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="501" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B501" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C501" s="11" t="s">
         <v>20</v>
@@ -14546,7 +14549,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="502" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="11" t="s">
         <v>29</v>
       </c>
@@ -14581,7 +14584,7 @@
         <v>15</v>
       </c>
       <c r="C503" s="11" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D503" s="12">
         <v>46235</v>
@@ -14589,8 +14592,12 @@
       <c r="E503" s="4">
         <v>1081600</v>
       </c>
-      <c r="F503" s="11"/>
-      <c r="G503" s="11"/>
+      <c r="F503" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G503" s="12">
+        <v>46286</v>
+      </c>
       <c r="H503" s="11" t="s">
         <v>7</v>
       </c>
@@ -14603,7 +14610,7 @@
         <v>15</v>
       </c>
       <c r="C504" s="11" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D504" s="12">
         <v>46235</v>
@@ -14611,8 +14618,12 @@
       <c r="E504" s="4">
         <v>292200</v>
       </c>
-      <c r="F504" s="11"/>
-      <c r="G504" s="11"/>
+      <c r="F504" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G504" s="12">
+        <v>46286</v>
+      </c>
       <c r="H504" s="11" t="s">
         <v>7</v>
       </c>
@@ -14625,7 +14636,7 @@
         <v>15</v>
       </c>
       <c r="C505" s="11" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D505" s="12">
         <v>46236</v>
@@ -14633,8 +14644,12 @@
       <c r="E505" s="4">
         <v>2016450</v>
       </c>
-      <c r="F505" s="11"/>
-      <c r="G505" s="11"/>
+      <c r="F505" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G505" s="12">
+        <v>46286</v>
+      </c>
       <c r="H505" s="11" t="s">
         <v>7</v>
       </c>
@@ -14647,7 +14662,7 @@
         <v>15</v>
       </c>
       <c r="C506" s="11" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D506" s="12">
         <v>46237</v>
@@ -14655,8 +14670,12 @@
       <c r="E506" s="4">
         <v>735300</v>
       </c>
-      <c r="F506" s="11"/>
-      <c r="G506" s="11"/>
+      <c r="F506" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G506" s="12">
+        <v>46286</v>
+      </c>
       <c r="H506" s="11" t="s">
         <v>7</v>
       </c>
@@ -14669,7 +14688,7 @@
         <v>15</v>
       </c>
       <c r="C507" s="11" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D507" s="12">
         <v>46239</v>
@@ -14677,13 +14696,17 @@
       <c r="E507" s="4">
         <v>549750</v>
       </c>
-      <c r="F507" s="11"/>
-      <c r="G507" s="11"/>
+      <c r="F507" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G507" s="12">
+        <v>46287</v>
+      </c>
       <c r="H507" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="508" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="11" t="s">
         <v>40</v>
       </c>
@@ -14717,7 +14740,7 @@
         <v>15</v>
       </c>
       <c r="C509" s="11" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D509" s="12">
         <v>46242</v>
@@ -14725,13 +14748,17 @@
       <c r="E509" s="4">
         <v>768026</v>
       </c>
-      <c r="F509" s="11"/>
-      <c r="G509" s="11"/>
+      <c r="F509" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G509" s="12">
+        <v>46287</v>
+      </c>
       <c r="H509" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="510" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="11" t="s">
         <v>29</v>
       </c>
@@ -14757,12 +14784,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="511" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="11" t="s">
         <v>29</v>
       </c>
       <c r="B511" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C511" s="11">
         <v>441358</v>
@@ -14784,12 +14811,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="512" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="11" t="s">
         <v>29</v>
       </c>
       <c r="B512" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C512" s="11">
         <v>441551</v>
@@ -14819,7 +14846,7 @@
         <v>15</v>
       </c>
       <c r="C513" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D513" s="12">
         <v>46243</v>
@@ -14827,13 +14854,17 @@
       <c r="E513" s="4">
         <v>838350</v>
       </c>
-      <c r="F513" s="11"/>
-      <c r="G513" s="11"/>
+      <c r="F513" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G513" s="12">
+        <v>46287</v>
+      </c>
       <c r="H513" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="514" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="11" t="s">
         <v>27</v>
       </c>
@@ -14865,7 +14896,7 @@
         <v>15</v>
       </c>
       <c r="C515" s="11" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D515" s="12">
         <v>46244</v>
@@ -14879,7 +14910,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="516" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="11" t="s">
         <v>30</v>
       </c>
@@ -14905,7 +14936,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="517" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="11" t="s">
         <v>26</v>
       </c>
@@ -14939,7 +14970,7 @@
         <v>15</v>
       </c>
       <c r="C518" s="11" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D518" s="12">
         <v>46247</v>
@@ -14953,7 +14984,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="519" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="11" t="s">
         <v>35</v>
       </c>
@@ -14979,7 +15010,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="520" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="11" t="s">
         <v>0</v>
       </c>
@@ -15000,7 +15031,7 @@
       <c r="G520" s="11"/>
       <c r="H520" s="11"/>
     </row>
-    <row r="521" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="11" t="s">
         <v>1</v>
       </c>
@@ -15021,7 +15052,7 @@
       <c r="G521" s="11"/>
       <c r="H521" s="11"/>
     </row>
-    <row r="522" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="11" t="s">
         <v>33</v>
       </c>
@@ -15041,7 +15072,7 @@
       <c r="G522" s="11"/>
       <c r="H522" s="11"/>
     </row>
-    <row r="523" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="11" t="s">
         <v>90</v>
       </c>
@@ -15061,12 +15092,12 @@
       <c r="G523" s="11"/>
       <c r="H523" s="11"/>
     </row>
-    <row r="524" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B524" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C524" s="11" t="s">
         <v>21</v>
@@ -15091,7 +15122,7 @@
         <v>15</v>
       </c>
       <c r="C525" s="11" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D525" s="12">
         <v>46250</v>
@@ -15113,7 +15144,7 @@
         <v>15</v>
       </c>
       <c r="C526" s="11" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D526" s="12">
         <v>46251</v>
@@ -15135,7 +15166,7 @@
         <v>15</v>
       </c>
       <c r="C527" s="11" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D527" s="12">
         <v>46256</v>
@@ -15157,7 +15188,7 @@
         <v>15</v>
       </c>
       <c r="C528" s="11" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D528" s="12">
         <v>46258</v>
@@ -15179,7 +15210,7 @@
         <v>15</v>
       </c>
       <c r="C529" s="11" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D529" s="12">
         <v>46260</v>
@@ -15201,7 +15232,7 @@
         <v>15</v>
       </c>
       <c r="C530" s="11" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D530" s="12">
         <v>46261</v>
@@ -15215,7 +15246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="531" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="11" t="s">
         <v>29</v>
       </c>
@@ -15241,7 +15272,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="532" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="11" t="s">
         <v>29</v>
       </c>
@@ -15267,7 +15298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="533" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="11" t="s">
         <v>29</v>
       </c>
@@ -15301,7 +15332,7 @@
         <v>15</v>
       </c>
       <c r="C534" s="11" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D534" s="12">
         <v>46262</v>
@@ -15323,7 +15354,7 @@
         <v>15</v>
       </c>
       <c r="C535" s="11" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D535" s="12">
         <v>46262</v>
@@ -15337,7 +15368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="536" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="11" t="s">
         <v>0</v>
       </c>
@@ -15358,7 +15389,7 @@
       <c r="G536" s="11"/>
       <c r="H536" s="11"/>
     </row>
-    <row r="537" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="11" t="s">
         <v>1</v>
       </c>
@@ -15379,7 +15410,7 @@
       <c r="G537" s="11"/>
       <c r="H537" s="11"/>
     </row>
-    <row r="538" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="11" t="s">
         <v>33</v>
       </c>
@@ -15399,7 +15430,7 @@
       <c r="G538" s="11"/>
       <c r="H538" s="11"/>
     </row>
-    <row r="539" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="11" t="s">
         <v>90</v>
       </c>
@@ -15419,12 +15450,12 @@
       <c r="G539" s="11"/>
       <c r="H539" s="11"/>
     </row>
-    <row r="540" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B540" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C540" s="11" t="s">
         <v>21</v>
@@ -15449,7 +15480,7 @@
         <v>15</v>
       </c>
       <c r="C541" s="11" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D541" s="12">
         <v>46265</v>
@@ -15471,7 +15502,7 @@
         <v>15</v>
       </c>
       <c r="C542" s="11" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D542" s="12">
         <v>46267</v>
@@ -15493,7 +15524,7 @@
         <v>15</v>
       </c>
       <c r="C543" s="11" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D543" s="12">
         <v>46268</v>
@@ -15507,7 +15538,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="544" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="11" t="s">
         <v>40</v>
       </c>
@@ -15533,7 +15564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="545" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="11" t="s">
         <v>29</v>
       </c>
@@ -15549,13 +15580,17 @@
       <c r="E545" s="4">
         <v>183824</v>
       </c>
-      <c r="F545" s="11"/>
-      <c r="G545" s="11"/>
+      <c r="F545" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G545" s="12">
+        <v>46279</v>
+      </c>
       <c r="H545" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="546" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="11" t="s">
         <v>29</v>
       </c>
@@ -15572,13 +15607,17 @@
         <f>93207*0.88</f>
         <v>82022.16</v>
       </c>
-      <c r="F546" s="11"/>
-      <c r="G546" s="11"/>
+      <c r="F546" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G546" s="12">
+        <v>46279</v>
+      </c>
       <c r="H546" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="547" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="11" t="s">
         <v>29</v>
       </c>
@@ -15595,8 +15634,12 @@
         <f>258575*0.88</f>
         <v>227546</v>
       </c>
-      <c r="F547" s="11"/>
-      <c r="G547" s="11"/>
+      <c r="F547" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G547" s="12">
+        <v>46279</v>
+      </c>
       <c r="H547" s="11" t="s">
         <v>7</v>
       </c>
@@ -15609,7 +15652,7 @@
         <v>15</v>
       </c>
       <c r="C548" s="11" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D548" s="12">
         <v>46272</v>
@@ -15631,7 +15674,7 @@
         <v>15</v>
       </c>
       <c r="C549" s="11" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D549" s="12">
         <v>46274</v>
@@ -15645,7 +15688,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="550" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="11" t="s">
         <v>30</v>
       </c>
@@ -15661,13 +15704,17 @@
       <c r="E550" s="4">
         <v>2499370</v>
       </c>
-      <c r="F550" s="11"/>
-      <c r="G550" s="11"/>
+      <c r="F550" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G550" s="12">
+        <v>46273</v>
+      </c>
       <c r="H550" s="11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="551" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="11" t="s">
         <v>29</v>
       </c>
@@ -15683,13 +15730,17 @@
       <c r="E551" s="8">
         <v>597212</v>
       </c>
-      <c r="F551" s="11"/>
-      <c r="G551" s="11"/>
+      <c r="F551" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G551" s="12">
+        <v>46279</v>
+      </c>
       <c r="H551" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="552" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="11" t="s">
         <v>29</v>
       </c>
@@ -15703,20 +15754,24 @@
         <v>46275</v>
       </c>
       <c r="E552" s="4">
-        <v>171955</v>
-      </c>
-      <c r="F552" s="11"/>
-      <c r="G552" s="11"/>
+        <v>185038</v>
+      </c>
+      <c r="F552" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G552" s="12">
+        <v>46280</v>
+      </c>
       <c r="H552" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="553" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="11" t="s">
         <v>29</v>
       </c>
       <c r="B553" s="11" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C553" s="11">
         <v>446844</v>
@@ -15727,13 +15782,17 @@
       <c r="E553" s="8">
         <v>775532</v>
       </c>
-      <c r="F553" s="11"/>
-      <c r="G553" s="11"/>
+      <c r="F553" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G553" s="12">
+        <v>46279</v>
+      </c>
       <c r="H553" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="554" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="11" t="s">
         <v>27</v>
       </c>
@@ -15758,10 +15817,10 @@
         <v>14</v>
       </c>
       <c r="B555" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C555" s="11" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="D555" s="12">
         <v>46276</v>
@@ -15783,7 +15842,7 @@
         <v>15</v>
       </c>
       <c r="C556" s="11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D556" s="12">
         <v>46279</v>
@@ -15797,7 +15856,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="557" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="11" t="s">
         <v>26</v>
       </c>
@@ -15819,7 +15878,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="558" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="11" t="s">
         <v>39</v>
       </c>
@@ -15837,9 +15896,11 @@
       </c>
       <c r="F558" s="11"/>
       <c r="G558" s="12"/>
-      <c r="H558" s="11"/>
-    </row>
-    <row r="559" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H558" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="559" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="11" t="s">
         <v>35</v>
       </c>
@@ -15859,7 +15920,7 @@
       <c r="G559" s="11"/>
       <c r="H559" s="11"/>
     </row>
-    <row r="560" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="11" t="s">
         <v>0</v>
       </c>
@@ -15880,7 +15941,7 @@
       <c r="G560" s="11"/>
       <c r="H560" s="11"/>
     </row>
-    <row r="561" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="11" t="s">
         <v>1</v>
       </c>
@@ -15901,7 +15962,7 @@
       <c r="G561" s="11"/>
       <c r="H561" s="11"/>
     </row>
-    <row r="562" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="11" t="s">
         <v>33</v>
       </c>
@@ -15921,7 +15982,7 @@
       <c r="G562" s="11"/>
       <c r="H562" s="11"/>
     </row>
-    <row r="563" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="11" t="s">
         <v>90</v>
       </c>
@@ -15941,12 +16002,12 @@
       <c r="G563" s="11"/>
       <c r="H563" s="11"/>
     </row>
-    <row r="564" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B564" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C564" s="11" t="s">
         <v>22</v>
@@ -15971,7 +16032,7 @@
         <v>15</v>
       </c>
       <c r="C565" s="11" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D565" s="12">
         <v>46282</v>
@@ -15993,7 +16054,7 @@
         <v>15</v>
       </c>
       <c r="C566" s="11" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D566" s="12">
         <v>46285</v>
@@ -16015,7 +16076,7 @@
         <v>15</v>
       </c>
       <c r="C567" s="11" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D567" s="12">
         <v>46288</v>
@@ -16029,7 +16090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="568" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="11" t="s">
         <v>29</v>
       </c>
@@ -16051,7 +16112,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="569" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="11" t="s">
         <v>29</v>
       </c>
@@ -16080,8 +16141,8 @@
       <c r="B570" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C570" s="30" t="s">
-        <v>248</v>
+      <c r="C570" s="33" t="s">
+        <v>256</v>
       </c>
       <c r="D570" s="12">
         <v>46292</v>
@@ -16095,7 +16156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="571" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="11" t="s">
         <v>29</v>
       </c>
@@ -16125,7 +16186,7 @@
         <v>15</v>
       </c>
       <c r="C572" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="D572" s="12">
         <v>46294</v>
@@ -16139,7 +16200,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="573" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="11" t="s">
         <v>0</v>
       </c>
@@ -16160,7 +16221,7 @@
       <c r="G573" s="11"/>
       <c r="H573" s="11"/>
     </row>
-    <row r="574" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="11" t="s">
         <v>1</v>
       </c>
@@ -16181,7 +16242,7 @@
       <c r="G574" s="11"/>
       <c r="H574" s="11"/>
     </row>
-    <row r="575" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="11" t="s">
         <v>33</v>
       </c>
@@ -16201,7 +16262,7 @@
       <c r="G575" s="11"/>
       <c r="H575" s="11"/>
     </row>
-    <row r="576" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="11" t="s">
         <v>90</v>
       </c>
@@ -16221,12 +16282,12 @@
       <c r="G576" s="11"/>
       <c r="H576" s="11"/>
     </row>
-    <row r="577" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="11" t="s">
         <v>118</v>
       </c>
       <c r="B577" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C577" s="11" t="s">
         <v>22</v>
@@ -16251,10 +16312,10 @@
         <v>15</v>
       </c>
       <c r="C578" s="11" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="D578" s="12">
-        <v>46297</v>
+        <v>46267</v>
       </c>
       <c r="E578" s="4">
         <v>614099</v>
@@ -16273,13 +16334,13 @@
         <v>15</v>
       </c>
       <c r="C579" s="11" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D579" s="12">
-        <v>46299</v>
+        <v>46303</v>
       </c>
       <c r="E579" s="4">
-        <v>745670</v>
+        <v>1433372</v>
       </c>
       <c r="F579" s="11"/>
       <c r="G579" s="11"/>
@@ -16289,61 +16350,63 @@
     </row>
     <row r="580" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="11" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B580" s="11" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C580" s="11" t="s">
-        <v>25</v>
+        <v>260</v>
       </c>
       <c r="D580" s="12">
-        <v>46300</v>
+        <v>46305</v>
       </c>
       <c r="E580" s="4">
-        <v>3000000</v>
+        <v>675709</v>
       </c>
       <c r="F580" s="11"/>
       <c r="G580" s="11"/>
       <c r="H580" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="581" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="11" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B581" s="11" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C581" s="11" t="s">
-        <v>25</v>
+        <v>258</v>
       </c>
       <c r="D581" s="12">
-        <v>46305</v>
+        <v>46299</v>
       </c>
       <c r="E581" s="4">
-        <v>100000</v>
+        <v>745670</v>
       </c>
       <c r="F581" s="11"/>
       <c r="G581" s="11"/>
-      <c r="H581" s="11"/>
-    </row>
-    <row r="582" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H581" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="582" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="11" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B582" s="11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C582" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D582" s="12">
-        <v>46306</v>
+        <v>46300</v>
       </c>
       <c r="E582" s="4">
-        <v>2603890</v>
+        <v>3000000</v>
       </c>
       <c r="F582" s="11"/>
       <c r="G582" s="11"/>
@@ -16351,75 +16414,76 @@
         <v>6</v>
       </c>
     </row>
-    <row r="583" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B583" s="11">
-        <v>894509</v>
+        <v>27</v>
+      </c>
+      <c r="B583" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="C583" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D583" s="12">
-        <v>46309</v>
+        <v>46305</v>
       </c>
       <c r="E583" s="4">
-        <v>370000</v>
+        <v>100000</v>
       </c>
       <c r="F583" s="11"/>
       <c r="G583" s="11"/>
-      <c r="H583" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="584" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H583" s="11"/>
+    </row>
+    <row r="584" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B584" s="11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C584" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D584" s="12">
-        <v>46310</v>
+        <v>46306</v>
       </c>
       <c r="E584" s="4">
-        <v>119400</v>
+        <v>2603890</v>
       </c>
       <c r="F584" s="11"/>
       <c r="G584" s="11"/>
-      <c r="H584" s="11"/>
-    </row>
-    <row r="585" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H584" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="585" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B585" s="11" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="B585" s="11">
+        <v>894509</v>
       </c>
       <c r="C585" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D585" s="12">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="E585" s="4">
-        <f>1083167*1.25</f>
-        <v>1353958.75</v>
+        <v>370000</v>
       </c>
       <c r="F585" s="11"/>
       <c r="G585" s="11"/>
-      <c r="H585" s="11"/>
-    </row>
-    <row r="586" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H585" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="586" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="11" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B586" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C586" s="11" t="s">
         <v>25</v>
@@ -16428,16 +16492,15 @@
         <v>46310</v>
       </c>
       <c r="E586" s="4">
-        <f>1083167*1.25</f>
-        <v>1353958.75</v>
+        <v>119400</v>
       </c>
       <c r="F586" s="11"/>
       <c r="G586" s="11"/>
       <c r="H586" s="11"/>
     </row>
-    <row r="587" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="11" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B587" s="11" t="s">
         <v>34</v>
@@ -16449,15 +16512,16 @@
         <v>46310</v>
       </c>
       <c r="E587" s="4">
-        <v>210000</v>
+        <f>1083167*1.25</f>
+        <v>1353958.75</v>
       </c>
       <c r="F587" s="11"/>
       <c r="G587" s="11"/>
       <c r="H587" s="11"/>
     </row>
-    <row r="588" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="11" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="B588" s="11" t="s">
         <v>34</v>
@@ -16469,18 +16533,19 @@
         <v>46310</v>
       </c>
       <c r="E588" s="4">
-        <v>210000</v>
+        <f>1083167*1.25</f>
+        <v>1353958.75</v>
       </c>
       <c r="F588" s="11"/>
       <c r="G588" s="11"/>
       <c r="H588" s="11"/>
     </row>
-    <row r="589" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="11" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="B589" s="11" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="C589" s="11" t="s">
         <v>25</v>
@@ -16489,17 +16554,15 @@
         <v>46310</v>
       </c>
       <c r="E589" s="4">
-        <v>500000</v>
+        <v>210000</v>
       </c>
       <c r="F589" s="11"/>
       <c r="G589" s="11"/>
-      <c r="H589" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="590" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H589" s="11"/>
+    </row>
+    <row r="590" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="11" t="s">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="B590" s="11" t="s">
         <v>34</v>
@@ -16508,60 +16571,61 @@
         <v>25</v>
       </c>
       <c r="D590" s="12">
-        <v>46325</v>
+        <v>46310</v>
       </c>
       <c r="E590" s="4">
-        <f>1083167*1.25</f>
-        <v>1353958.75</v>
+        <v>210000</v>
       </c>
       <c r="F590" s="11"/>
       <c r="G590" s="11"/>
       <c r="H590" s="11"/>
     </row>
-    <row r="591" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="11" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="B591" s="11" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="C591" s="11" t="s">
         <v>25</v>
       </c>
       <c r="D591" s="12">
+        <v>46310</v>
+      </c>
+      <c r="E591" s="4">
+        <v>500000</v>
+      </c>
+      <c r="F591" s="11"/>
+      <c r="G591" s="11"/>
+      <c r="H591" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="592" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A592" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B592" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C592" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D592" s="12">
         <v>46325</v>
       </c>
-      <c r="E591" s="4">
+      <c r="E592" s="4">
         <f>1083167*1.25</f>
         <v>1353958.75</v>
-      </c>
-      <c r="F591" s="11"/>
-      <c r="G591" s="11"/>
-      <c r="H591" s="11"/>
-    </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A592" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B592" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C592" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D592" s="12">
-        <v>46325</v>
-      </c>
-      <c r="E592" s="4">
-        <v>210000</v>
       </c>
       <c r="F592" s="11"/>
       <c r="G592" s="11"/>
       <c r="H592" s="11"/>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="11" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="B593" s="11" t="s">
         <v>34</v>
@@ -16573,18 +16637,19 @@
         <v>46325</v>
       </c>
       <c r="E593" s="4">
-        <v>210000</v>
+        <f>1083167*1.25</f>
+        <v>1353958.75</v>
       </c>
       <c r="F593" s="11"/>
       <c r="G593" s="11"/>
       <c r="H593" s="11"/>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="11" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="B594" s="11" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="C594" s="11" t="s">
         <v>25</v>
@@ -16593,71 +16658,69 @@
         <v>46325</v>
       </c>
       <c r="E594" s="4">
-        <v>500000</v>
+        <v>210000</v>
       </c>
       <c r="F594" s="11"/>
       <c r="G594" s="11"/>
-      <c r="H594" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H594" s="11"/>
+    </row>
+    <row r="595" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="11" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B595" s="11" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C595" s="11" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D595" s="12">
-        <v>46331</v>
+        <v>46325</v>
       </c>
       <c r="E595" s="4">
-        <v>3000000</v>
+        <v>210000</v>
       </c>
       <c r="F595" s="11"/>
       <c r="G595" s="11"/>
-      <c r="H595" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H595" s="11"/>
+    </row>
+    <row r="596" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="11" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="B596" s="11" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="C596" s="11" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D596" s="12">
-        <v>46336</v>
+        <v>46325</v>
       </c>
       <c r="E596" s="4">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="F596" s="11"/>
       <c r="G596" s="11"/>
-      <c r="H596" s="11"/>
-    </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H596" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="597" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="11" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B597" s="11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C597" s="11" t="s">
         <v>42</v>
       </c>
       <c r="D597" s="12">
-        <v>46337</v>
+        <v>46331</v>
       </c>
       <c r="E597" s="4">
-        <v>2603890</v>
+        <v>3000000</v>
       </c>
       <c r="F597" s="11"/>
       <c r="G597" s="11"/>
@@ -16665,75 +16728,76 @@
         <v>6</v>
       </c>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B598" s="11">
-        <v>894509</v>
+        <v>27</v>
+      </c>
+      <c r="B598" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="C598" s="11" t="s">
         <v>42</v>
       </c>
       <c r="D598" s="12">
-        <v>46340</v>
+        <v>46336</v>
       </c>
       <c r="E598" s="4">
-        <v>370000</v>
+        <v>100000</v>
       </c>
       <c r="F598" s="11"/>
       <c r="G598" s="11"/>
-      <c r="H598" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H598" s="11"/>
+    </row>
+    <row r="599" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B599" s="11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C599" s="11" t="s">
         <v>42</v>
       </c>
       <c r="D599" s="12">
-        <v>46341</v>
+        <v>46337</v>
       </c>
       <c r="E599" s="4">
-        <v>119400</v>
+        <v>2603890</v>
       </c>
       <c r="F599" s="11"/>
       <c r="G599" s="11"/>
-      <c r="H599" s="11"/>
-    </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H599" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="600" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B600" s="11" t="s">
-        <v>34</v>
+        <v>26</v>
+      </c>
+      <c r="B600" s="11">
+        <v>894509</v>
       </c>
       <c r="C600" s="11" t="s">
         <v>42</v>
       </c>
       <c r="D600" s="12">
-        <v>46341</v>
+        <v>46340</v>
       </c>
       <c r="E600" s="4">
-        <f>1083167*1.25</f>
-        <v>1353958.75</v>
+        <v>370000</v>
       </c>
       <c r="F600" s="11"/>
       <c r="G600" s="11"/>
-      <c r="H600" s="11"/>
-    </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H600" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="11" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B601" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C601" s="11" t="s">
         <v>42</v>
@@ -16742,16 +16806,15 @@
         <v>46341</v>
       </c>
       <c r="E601" s="4">
-        <f>1083167*1.25</f>
-        <v>1353958.75</v>
+        <v>119400</v>
       </c>
       <c r="F601" s="11"/>
       <c r="G601" s="11"/>
       <c r="H601" s="11"/>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="11" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B602" s="11" t="s">
         <v>34</v>
@@ -16763,15 +16826,16 @@
         <v>46341</v>
       </c>
       <c r="E602" s="4">
-        <v>210000</v>
+        <f>1083167*1.25</f>
+        <v>1353958.75</v>
       </c>
       <c r="F602" s="11"/>
       <c r="G602" s="11"/>
       <c r="H602" s="11"/>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="11" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="B603" s="11" t="s">
         <v>34</v>
@@ -16783,18 +16847,19 @@
         <v>46341</v>
       </c>
       <c r="E603" s="4">
-        <v>210000</v>
+        <f>1083167*1.25</f>
+        <v>1353958.75</v>
       </c>
       <c r="F603" s="11"/>
       <c r="G603" s="11"/>
       <c r="H603" s="11"/>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="11" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="B604" s="11" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="C604" s="11" t="s">
         <v>42</v>
@@ -16803,17 +16868,15 @@
         <v>46341</v>
       </c>
       <c r="E604" s="4">
-        <v>500000</v>
+        <v>210000</v>
       </c>
       <c r="F604" s="11"/>
       <c r="G604" s="11"/>
-      <c r="H604" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H604" s="11"/>
+    </row>
+    <row r="605" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="11" t="s">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="B605" s="11" t="s">
         <v>34</v>
@@ -16822,60 +16885,61 @@
         <v>42</v>
       </c>
       <c r="D605" s="12">
-        <v>46356</v>
+        <v>46341</v>
       </c>
       <c r="E605" s="4">
-        <f>1083167*1.25</f>
-        <v>1353958.75</v>
+        <v>210000</v>
       </c>
       <c r="F605" s="11"/>
       <c r="G605" s="11"/>
       <c r="H605" s="11"/>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="11" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="B606" s="11" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="C606" s="11" t="s">
         <v>42</v>
       </c>
       <c r="D606" s="12">
+        <v>46341</v>
+      </c>
+      <c r="E606" s="4">
+        <v>500000</v>
+      </c>
+      <c r="F606" s="11"/>
+      <c r="G606" s="11"/>
+      <c r="H606" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="607" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A607" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B607" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C607" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D607" s="12">
         <v>46356</v>
       </c>
-      <c r="E606" s="4">
+      <c r="E607" s="4">
         <f>1083167*1.25</f>
         <v>1353958.75</v>
-      </c>
-      <c r="F606" s="11"/>
-      <c r="G606" s="11"/>
-      <c r="H606" s="11"/>
-    </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A607" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B607" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C607" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D607" s="12">
-        <v>46356</v>
-      </c>
-      <c r="E607" s="4">
-        <v>210000</v>
       </c>
       <c r="F607" s="11"/>
       <c r="G607" s="11"/>
       <c r="H607" s="11"/>
     </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="11" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="B608" s="11" t="s">
         <v>34</v>
@@ -16887,18 +16951,19 @@
         <v>46356</v>
       </c>
       <c r="E608" s="4">
-        <v>210000</v>
+        <f>1083167*1.25</f>
+        <v>1353958.75</v>
       </c>
       <c r="F608" s="11"/>
       <c r="G608" s="11"/>
       <c r="H608" s="11"/>
     </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="11" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="B609" s="11" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="C609" s="11" t="s">
         <v>42</v>
@@ -16907,71 +16972,69 @@
         <v>46356</v>
       </c>
       <c r="E609" s="4">
-        <v>500000</v>
+        <v>210000</v>
       </c>
       <c r="F609" s="11"/>
       <c r="G609" s="11"/>
-      <c r="H609" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H609" s="11"/>
+    </row>
+    <row r="610" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="11" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B610" s="11" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C610" s="11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D610" s="12">
-        <v>46361</v>
+        <v>46356</v>
       </c>
       <c r="E610" s="4">
-        <v>3000000</v>
+        <v>210000</v>
       </c>
       <c r="F610" s="11"/>
       <c r="G610" s="11"/>
-      <c r="H610" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H610" s="11"/>
+    </row>
+    <row r="611" spans="1:8" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="11" t="s">
-        <v>27</v>
+        <v>118</v>
       </c>
       <c r="B611" s="11" t="s">
-        <v>28</v>
+        <v>130</v>
       </c>
       <c r="C611" s="11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D611" s="12">
-        <v>46366</v>
+        <v>46356</v>
       </c>
       <c r="E611" s="4">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="F611" s="11"/>
       <c r="G611" s="11"/>
-      <c r="H611" s="11"/>
-    </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H611" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="11" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B612" s="11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C612" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D612" s="12">
-        <v>46367</v>
+        <v>46361</v>
       </c>
       <c r="E612" s="4">
-        <v>2603890</v>
+        <v>3000000</v>
       </c>
       <c r="F612" s="11"/>
       <c r="G612" s="11"/>
@@ -16979,74 +17042,76 @@
         <v>6</v>
       </c>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B613" s="11">
-        <v>894509</v>
+        <v>27</v>
+      </c>
+      <c r="B613" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="C613" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D613" s="12">
-        <v>46370</v>
+        <v>46366</v>
       </c>
       <c r="E613" s="4">
-        <v>370000</v>
+        <v>100000</v>
       </c>
       <c r="F613" s="11"/>
       <c r="G613" s="11"/>
-      <c r="H613" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H613" s="11"/>
+    </row>
+    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="11" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B614" s="11" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="C614" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D614" s="12">
-        <v>46371</v>
+        <v>46367</v>
       </c>
       <c r="E614" s="4">
-        <v>1000000</v>
+        <v>2603890</v>
       </c>
       <c r="F614" s="11"/>
       <c r="G614" s="11"/>
-      <c r="H614" s="11"/>
-    </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H614" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B615" s="11" t="s">
-        <v>52</v>
+        <v>26</v>
+      </c>
+      <c r="B615" s="11">
+        <v>894509</v>
       </c>
       <c r="C615" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D615" s="12">
-        <v>46371</v>
+        <v>46370</v>
       </c>
       <c r="E615" s="4">
-        <v>1000000</v>
+        <v>370000</v>
       </c>
       <c r="F615" s="11"/>
       <c r="G615" s="11"/>
-      <c r="H615" s="11"/>
-    </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H615" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="11" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B616" s="11" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="C616" s="11" t="s">
         <v>50</v>
@@ -17055,18 +17120,18 @@
         <v>46371</v>
       </c>
       <c r="E616" s="4">
-        <v>119400</v>
+        <v>1000000</v>
       </c>
       <c r="F616" s="11"/>
       <c r="G616" s="11"/>
       <c r="H616" s="11"/>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="11" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B617" s="11" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C617" s="11" t="s">
         <v>50</v>
@@ -17075,19 +17140,18 @@
         <v>46371</v>
       </c>
       <c r="E617" s="4">
-        <f>1083167*1.25</f>
-        <v>1353958.75</v>
+        <v>1000000</v>
       </c>
       <c r="F617" s="11"/>
       <c r="G617" s="11"/>
       <c r="H617" s="11"/>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="11" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="B618" s="11" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C618" s="11" t="s">
         <v>50</v>
@@ -17096,16 +17160,15 @@
         <v>46371</v>
       </c>
       <c r="E618" s="4">
-        <f>1083167*1.25</f>
-        <v>1353958.75</v>
+        <v>119400</v>
       </c>
       <c r="F618" s="11"/>
       <c r="G618" s="11"/>
       <c r="H618" s="11"/>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="11" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B619" s="11" t="s">
         <v>34</v>
@@ -17117,15 +17180,16 @@
         <v>46371</v>
       </c>
       <c r="E619" s="4">
-        <v>210000</v>
+        <f>1083167*1.25</f>
+        <v>1353958.75</v>
       </c>
       <c r="F619" s="11"/>
       <c r="G619" s="11"/>
       <c r="H619" s="11"/>
     </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="11" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="B620" s="11" t="s">
         <v>34</v>
@@ -17137,18 +17201,19 @@
         <v>46371</v>
       </c>
       <c r="E620" s="4">
-        <v>210000</v>
+        <f>1083167*1.25</f>
+        <v>1353958.75</v>
       </c>
       <c r="F620" s="11"/>
       <c r="G620" s="11"/>
       <c r="H620" s="11"/>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="11" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="B621" s="11" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="C621" s="11" t="s">
         <v>50</v>
@@ -17157,17 +17222,15 @@
         <v>46371</v>
       </c>
       <c r="E621" s="4">
-        <v>500000</v>
+        <v>210000</v>
       </c>
       <c r="F621" s="11"/>
       <c r="G621" s="11"/>
-      <c r="H621" s="11" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H621" s="11"/>
+    </row>
+    <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="11" t="s">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="B622" s="11" t="s">
         <v>34</v>
@@ -17176,60 +17239,61 @@
         <v>50</v>
       </c>
       <c r="D622" s="12">
-        <v>46386</v>
+        <v>46371</v>
       </c>
       <c r="E622" s="4">
-        <f>1083167*1.25</f>
-        <v>1353958.75</v>
+        <v>210000</v>
       </c>
       <c r="F622" s="11"/>
       <c r="G622" s="11"/>
       <c r="H622" s="11"/>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="11" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="B623" s="11" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="C623" s="11" t="s">
         <v>50</v>
       </c>
       <c r="D623" s="12">
+        <v>46371</v>
+      </c>
+      <c r="E623" s="4">
+        <v>500000</v>
+      </c>
+      <c r="F623" s="11"/>
+      <c r="G623" s="11"/>
+      <c r="H623" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A624" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B624" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C624" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D624" s="12">
         <v>46386</v>
       </c>
-      <c r="E623" s="4">
+      <c r="E624" s="4">
         <f>1083167*1.25</f>
         <v>1353958.75</v>
-      </c>
-      <c r="F623" s="11"/>
-      <c r="G623" s="11"/>
-      <c r="H623" s="11"/>
-    </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A624" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="B624" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C624" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D624" s="12">
-        <v>46386</v>
-      </c>
-      <c r="E624" s="4">
-        <v>210000</v>
       </c>
       <c r="F624" s="11"/>
       <c r="G624" s="11"/>
       <c r="H624" s="11"/>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="11" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="B625" s="11" t="s">
         <v>34</v>
@@ -17241,18 +17305,19 @@
         <v>46386</v>
       </c>
       <c r="E625" s="4">
-        <v>210000</v>
+        <f>1083167*1.25</f>
+        <v>1353958.75</v>
       </c>
       <c r="F625" s="11"/>
       <c r="G625" s="11"/>
       <c r="H625" s="11"/>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="11" t="s">
-        <v>118</v>
+        <v>33</v>
       </c>
       <c r="B626" s="11" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
       <c r="C626" s="11" t="s">
         <v>50</v>
@@ -17261,113 +17326,129 @@
         <v>46386</v>
       </c>
       <c r="E626" s="4">
-        <v>500000</v>
+        <v>210000</v>
       </c>
       <c r="F626" s="11"/>
       <c r="G626" s="11"/>
-      <c r="H626" s="11" t="s">
+      <c r="H626" s="11"/>
+    </row>
+    <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A627" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B627" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C627" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D627" s="12">
+        <v>46386</v>
+      </c>
+      <c r="E627" s="4">
+        <v>210000</v>
+      </c>
+      <c r="F627" s="11"/>
+      <c r="G627" s="11"/>
+      <c r="H627" s="11"/>
+    </row>
+    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A628" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B628" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C628" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D628" s="12">
+        <v>46386</v>
+      </c>
+      <c r="E628" s="4">
+        <v>500000</v>
+      </c>
+      <c r="F628" s="11"/>
+      <c r="G628" s="11"/>
+      <c r="H628" s="11" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A627" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B627" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="C627" s="32" t="s">
-        <v>241</v>
-      </c>
-      <c r="D627" s="12">
-        <v>46199</v>
-      </c>
-      <c r="E627" s="25">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A629" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B629" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C629" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="D629" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="E629" s="25">
         <v>376450</v>
       </c>
-      <c r="F627" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="G627" s="12">
+      <c r="F629" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G629" s="12">
         <v>46253</v>
       </c>
-      <c r="H627" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A628" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B628" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="C628" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="D628" s="12">
-        <v>46199</v>
-      </c>
-      <c r="E628" s="25">
+      <c r="H629" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A630" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B630" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C630" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="D630" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="E630" s="25">
         <v>375050</v>
       </c>
-      <c r="F628" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="G628" s="12">
+      <c r="F630" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="G630" s="12">
         <v>46253</v>
       </c>
-      <c r="H628" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A629" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B629" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C629" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="D629" s="12">
-        <v>46295</v>
-      </c>
-      <c r="E629" s="4">
+      <c r="H630" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A631" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B631" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C631" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D631" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="E631" s="4">
         <v>1147390</v>
       </c>
-      <c r="F629" s="11"/>
-      <c r="G629" s="11"/>
-      <c r="H629" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A630" s="11"/>
-      <c r="B630" s="11"/>
-      <c r="C630" s="11"/>
-      <c r="D630" s="12"/>
-      <c r="E630" s="4"/>
-      <c r="F630" s="11"/>
-      <c r="G630" s="11"/>
-      <c r="H630" s="11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A631" s="11"/>
-      <c r="B631" s="11"/>
-      <c r="C631" s="11"/>
-      <c r="D631" s="12"/>
-      <c r="E631" s="4"/>
       <c r="F631" s="11"/>
       <c r="G631" s="11"/>
       <c r="H631" s="11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="11"/>
       <c r="B632" s="11"/>
       <c r="C632" s="11"/>
@@ -17375,9 +17456,11 @@
       <c r="E632" s="4"/>
       <c r="F632" s="11"/>
       <c r="G632" s="11"/>
-      <c r="H632" s="11"/>
-    </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H632" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="11"/>
       <c r="B633" s="11"/>
       <c r="C633" s="11"/>
@@ -17385,9 +17468,11 @@
       <c r="E633" s="4"/>
       <c r="F633" s="11"/>
       <c r="G633" s="11"/>
-      <c r="H633" s="11"/>
-    </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H633" s="11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="11"/>
       <c r="B634" s="11"/>
       <c r="C634" s="11"/>
@@ -17397,64 +17482,142 @@
       <c r="G634" s="11"/>
       <c r="H634" s="11"/>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="11"/>
       <c r="B635" s="11"/>
       <c r="C635" s="11"/>
-      <c r="D635" s="11"/>
-      <c r="E635" s="4">
-        <v>0</v>
-      </c>
+      <c r="D635" s="12"/>
+      <c r="E635" s="4"/>
       <c r="F635" s="11"/>
       <c r="G635" s="11"/>
       <c r="H635" s="11"/>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="E636" s="6"/>
-    </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D637" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="E637" s="10">
-        <f>SUBTOTAL(9,E2:E611)</f>
-        <v>510274617.57199997</v>
-      </c>
+    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A636" s="11"/>
+      <c r="B636" s="11"/>
+      <c r="C636" s="11"/>
+      <c r="D636" s="12"/>
+      <c r="E636" s="4"/>
+      <c r="F636" s="11"/>
+      <c r="G636" s="11"/>
+      <c r="H636" s="11"/>
+    </row>
+    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A637" s="11"/>
+      <c r="B637" s="11"/>
+      <c r="C637" s="11"/>
+      <c r="D637" s="11"/>
+      <c r="E637" s="4">
+        <v>0</v>
+      </c>
+      <c r="F637" s="11"/>
+      <c r="G637" s="11"/>
+      <c r="H637" s="11"/>
+    </row>
+    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E638" s="6"/>
     </row>
     <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="D639" s="10" t="s">
-        <v>254</v>
+        <v>120</v>
       </c>
       <c r="E639" s="10">
-        <f>E637+[1]Hoja1!E81</f>
-        <v>520428350.57199997</v>
-      </c>
-    </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D640" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E640" s="10">
+        <f>SUBTOTAL(9,E2:E613)</f>
+        <v>263040875.79000002</v>
+      </c>
+    </row>
+    <row r="641" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D641" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="E641" s="10" t="e">
+        <f>E639+#REF!</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="642" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D642" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E642" s="10">
         <v>32217552</v>
       </c>
     </row>
-    <row r="641" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D641" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E641" s="10">
-        <f>E640-E639</f>
-        <v>-488210798.57199997</v>
+    <row r="643" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D643" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E643" s="10" t="e">
+        <f>E642-E641</f>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H617" xr:uid="{07263182-CB96-42D2-A98F-26F97CC8FA02}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H617">
-      <sortCondition ref="D1:D617"/>
+  <autoFilter ref="A1:H637" xr:uid="{07263182-CB96-42D2-A98F-26F97CC8FA02}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Invervisa"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H637">
+      <sortCondition ref="D1:D637"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A4F2FD81-44E9-4D83-B16C-AAEC647EFBE9}">
+          <x14:formula1>
+            <xm:f>'NO TOCAR'!$E$1:$E$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H28 H618:H619 H631 H66:H612</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DB82DB46-F8C0-4E43-B347-8DCEB1E8268A}">
+          <x14:formula1>
+            <xm:f>'NO TOCAR'!$C$1:$C$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F29 F234:F284 F32:F232 F286:F612</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01F2EA59-99CA-4C83-9106-A4A9A95FC1B9}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>